--- a/docentes/González Sánchez Rene Aurelio - Estadisticos 20212.xlsx
+++ b/docentes/González Sánchez Rene Aurelio - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="242">
   <si>
     <t>Mat</t>
   </si>
@@ -154,6 +154,123 @@
     <t>XOTLANIHUA</t>
   </si>
   <si>
+    <t>ANDRADE</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>ARROYO</t>
+  </si>
+  <si>
+    <t>BASILIO</t>
+  </si>
+  <si>
+    <t>BUSTOS</t>
+  </si>
+  <si>
+    <t>DEMUNER</t>
+  </si>
+  <si>
+    <t>GASCA</t>
+  </si>
+  <si>
+    <t>GUERRA</t>
+  </si>
+  <si>
+    <t>HUESCA</t>
+  </si>
+  <si>
+    <t>LORENZO</t>
+  </si>
+  <si>
+    <t>LOBATO</t>
+  </si>
+  <si>
+    <t>MATA</t>
+  </si>
+  <si>
+    <t>PARRA</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>RICO</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>VELAZQEZ</t>
+  </si>
+  <si>
+    <t>XOCUA</t>
+  </si>
+  <si>
+    <t>ZUÑIGA</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>LIMON</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MARCIAL</t>
+  </si>
+  <si>
+    <t>MAYAHUA</t>
+  </si>
+  <si>
+    <t>OLIVARES</t>
+  </si>
+  <si>
+    <t>OSORIO</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>DE LA ROSA</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>AMADOR</t>
+  </si>
+  <si>
+    <t>CITALAN</t>
+  </si>
+  <si>
+    <t>CID</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>MENDIZABAL</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>TELLEZ</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
     <t>CONGUILLO</t>
   </si>
   <si>
@@ -169,15 +286,24 @@
     <t>TIBURCIO</t>
   </si>
   <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>GUEVARA</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
     <t>CIRUELO</t>
   </si>
   <si>
     <t>TEQUIHUATLE</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
     <t>CONDE</t>
   </si>
   <si>
@@ -196,27 +322,15 @@
     <t>ENRIQUEZ</t>
   </si>
   <si>
-    <t>LORENZO</t>
-  </si>
-  <si>
     <t>SANTES</t>
   </si>
   <si>
     <t>MARINERO</t>
   </si>
   <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
     <t>OFICIAL</t>
   </si>
   <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
     <t>PEREZ</t>
   </si>
   <si>
@@ -229,6 +343,93 @@
     <t>TETLA</t>
   </si>
   <si>
+    <t>MONTALVO</t>
+  </si>
+  <si>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>ALONSO</t>
+  </si>
+  <si>
+    <t>JERONIMO</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>MIXCOA</t>
+  </si>
+  <si>
+    <t>CANSECO</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>MELO</t>
+  </si>
+  <si>
+    <t>VICTORIANO</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>ROMANOS</t>
+  </si>
+  <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
+    <t>NOYOLA</t>
+  </si>
+  <si>
+    <t>XOCHIQUISQUI</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>MACHORRO</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>PORRAS</t>
+  </si>
+  <si>
+    <t>VALENCIA</t>
+  </si>
+  <si>
+    <t>SEGURA</t>
+  </si>
+  <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
     <t>ZOPIYACTLE</t>
   </si>
   <si>
@@ -244,6 +445,21 @@
     <t>ORTEGA</t>
   </si>
   <si>
+    <t>GARCÍA</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>MARROQUIN</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>BELLO</t>
+  </si>
+  <si>
     <t>FATIMA</t>
   </si>
   <si>
@@ -325,6 +541,156 @@
     <t>ERIKA</t>
   </si>
   <si>
+    <t>PATRICIA</t>
+  </si>
+  <si>
+    <t>LUIS YAEL</t>
+  </si>
+  <si>
+    <t>VICTOR HUGO</t>
+  </si>
+  <si>
+    <t>VANESA</t>
+  </si>
+  <si>
+    <t>SARAHI</t>
+  </si>
+  <si>
+    <t>ADRIANA ARELY</t>
+  </si>
+  <si>
+    <t>ARANTXA</t>
+  </si>
+  <si>
+    <t>MARIA YAZMIN</t>
+  </si>
+  <si>
+    <t>JAEL SAMAI</t>
+  </si>
+  <si>
+    <t>LIZBET</t>
+  </si>
+  <si>
+    <t>XIMENA</t>
+  </si>
+  <si>
+    <t>ALDAIR OMAR</t>
+  </si>
+  <si>
+    <t>GUADALUPE</t>
+  </si>
+  <si>
+    <t>DANIELA RUBI</t>
+  </si>
+  <si>
+    <t>CRISTIAN ARTURO</t>
+  </si>
+  <si>
+    <t>SUEMI</t>
+  </si>
+  <si>
+    <t>ESTHER ARISBETH</t>
+  </si>
+  <si>
+    <t>JAROMI YAJAIRA</t>
+  </si>
+  <si>
+    <t>EDGAR RAMSES</t>
+  </si>
+  <si>
+    <t>BERENICE</t>
+  </si>
+  <si>
+    <t>IRIS VIANNEY</t>
+  </si>
+  <si>
+    <t>MARIAN</t>
+  </si>
+  <si>
+    <t>PAULINA</t>
+  </si>
+  <si>
+    <t>AYARI</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
+    <t>MELANIE NAOMI</t>
+  </si>
+  <si>
+    <t>AMARANTA DENISSE</t>
+  </si>
+  <si>
+    <t>KIMBERLY ALONDRA</t>
+  </si>
+  <si>
+    <t>MARIJOSE</t>
+  </si>
+  <si>
+    <t>MARIA JOSE</t>
+  </si>
+  <si>
+    <t>ABDIEL</t>
+  </si>
+  <si>
+    <t>IVAN DE JESUS</t>
+  </si>
+  <si>
+    <t>DAMARIS</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>KARLA</t>
+  </si>
+  <si>
+    <t>INGRID YALITH</t>
+  </si>
+  <si>
+    <t>LUCERO</t>
+  </si>
+  <si>
+    <t>ALONDRA</t>
+  </si>
+  <si>
+    <t>KIMBERLY</t>
+  </si>
+  <si>
+    <t>FRANCISCO ALAN</t>
+  </si>
+  <si>
+    <t>MISAEL</t>
+  </si>
+  <si>
+    <t>JESUS</t>
+  </si>
+  <si>
+    <t>BRUNO AZAEL</t>
+  </si>
+  <si>
+    <t>CESAR</t>
+  </si>
+  <si>
+    <t>ROBERTO</t>
+  </si>
+  <si>
+    <t>ALDER ALBERTO</t>
+  </si>
+  <si>
+    <t>SERGIO MARIANO</t>
+  </si>
+  <si>
+    <t>ROSA ISELA</t>
+  </si>
+  <si>
+    <t>BENY ALEXANDER</t>
+  </si>
+  <si>
+    <t>GUILLERMO</t>
+  </si>
+  <si>
     <t>CONSUELO DALILA</t>
   </si>
   <si>
@@ -350,6 +716,33 @@
   </si>
   <si>
     <t>DIANA VIANNEY</t>
+  </si>
+  <si>
+    <t>RAUL</t>
+  </si>
+  <si>
+    <t>DAVID</t>
+  </si>
+  <si>
+    <t>YAHIR</t>
+  </si>
+  <si>
+    <t>MARIA ASUNCION</t>
+  </si>
+  <si>
+    <t>NOEL ALBERTO</t>
+  </si>
+  <si>
+    <t>LUIS ALBERTO</t>
+  </si>
+  <si>
+    <t>ZURIEL ARTURO</t>
+  </si>
+  <si>
+    <t>JUAN CARLOS</t>
+  </si>
+  <si>
+    <t>CESAR OMAR</t>
   </si>
 </sst>
 </file>
@@ -1238,7 +1631,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G98"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1276,10 +1669,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>50</v>
+        <v>93</v>
       </c>
       <c r="D2" t="s">
-        <v>75</v>
+        <v>147</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -1302,7 +1695,7 @@
         <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>76</v>
+        <v>148</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -1322,10 +1715,10 @@
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>51</v>
+        <v>94</v>
       </c>
       <c r="D4" t="s">
-        <v>77</v>
+        <v>149</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -1345,10 +1738,10 @@
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>52</v>
+        <v>92</v>
       </c>
       <c r="D5" t="s">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -1368,10 +1761,10 @@
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>53</v>
+        <v>95</v>
       </c>
       <c r="D6" t="s">
-        <v>79</v>
+        <v>151</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -1391,10 +1784,10 @@
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>54</v>
+        <v>96</v>
       </c>
       <c r="D7" t="s">
-        <v>80</v>
+        <v>152</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -1417,7 +1810,7 @@
         <v>26</v>
       </c>
       <c r="D8" t="s">
-        <v>81</v>
+        <v>153</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -1437,10 +1830,10 @@
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>55</v>
+        <v>97</v>
       </c>
       <c r="D9" t="s">
-        <v>82</v>
+        <v>154</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -1460,10 +1853,10 @@
         <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>56</v>
+        <v>98</v>
       </c>
       <c r="D10" t="s">
-        <v>83</v>
+        <v>155</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -1483,10 +1876,10 @@
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>57</v>
+        <v>99</v>
       </c>
       <c r="D11" t="s">
-        <v>84</v>
+        <v>156</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -1506,10 +1899,10 @@
         <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>58</v>
+        <v>100</v>
       </c>
       <c r="D12" t="s">
-        <v>85</v>
+        <v>157</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
@@ -1529,10 +1922,10 @@
         <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D13" t="s">
-        <v>86</v>
+        <v>158</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
@@ -1552,10 +1945,10 @@
         <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>60</v>
+        <v>101</v>
       </c>
       <c r="D14" t="s">
-        <v>87</v>
+        <v>159</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
@@ -1575,10 +1968,10 @@
         <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>61</v>
+        <v>102</v>
       </c>
       <c r="D15" t="s">
-        <v>88</v>
+        <v>160</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
@@ -1598,10 +1991,10 @@
         <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D16" t="s">
-        <v>89</v>
+        <v>161</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
@@ -1624,7 +2017,7 @@
         <v>25</v>
       </c>
       <c r="D17" t="s">
-        <v>90</v>
+        <v>162</v>
       </c>
       <c r="E17" t="s">
         <v>9</v>
@@ -1644,10 +2037,10 @@
         <v>35</v>
       </c>
       <c r="C18" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D18" t="s">
-        <v>91</v>
+        <v>163</v>
       </c>
       <c r="E18" t="s">
         <v>9</v>
@@ -1670,7 +2063,7 @@
         <v>28</v>
       </c>
       <c r="D19" t="s">
-        <v>92</v>
+        <v>164</v>
       </c>
       <c r="E19" t="s">
         <v>9</v>
@@ -1690,10 +2083,10 @@
         <v>38</v>
       </c>
       <c r="C20" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D20" t="s">
-        <v>93</v>
+        <v>165</v>
       </c>
       <c r="E20" t="s">
         <v>9</v>
@@ -1716,7 +2109,7 @@
         <v>31</v>
       </c>
       <c r="D21" t="s">
-        <v>94</v>
+        <v>166</v>
       </c>
       <c r="E21" t="s">
         <v>9</v>
@@ -1736,10 +2129,10 @@
         <v>39</v>
       </c>
       <c r="C22" t="s">
-        <v>64</v>
+        <v>103</v>
       </c>
       <c r="D22" t="s">
-        <v>95</v>
+        <v>167</v>
       </c>
       <c r="E22" t="s">
         <v>9</v>
@@ -1759,10 +2152,10 @@
         <v>40</v>
       </c>
       <c r="C23" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="D23" t="s">
-        <v>96</v>
+        <v>168</v>
       </c>
       <c r="E23" t="s">
         <v>9</v>
@@ -1782,10 +2175,10 @@
         <v>41</v>
       </c>
       <c r="C24" t="s">
-        <v>66</v>
+        <v>104</v>
       </c>
       <c r="D24" t="s">
-        <v>97</v>
+        <v>169</v>
       </c>
       <c r="E24" t="s">
         <v>9</v>
@@ -1805,10 +2198,10 @@
         <v>41</v>
       </c>
       <c r="C25" t="s">
-        <v>67</v>
+        <v>105</v>
       </c>
       <c r="D25" t="s">
-        <v>98</v>
+        <v>170</v>
       </c>
       <c r="E25" t="s">
         <v>9</v>
@@ -1828,10 +2221,10 @@
         <v>42</v>
       </c>
       <c r="C26" t="s">
-        <v>68</v>
+        <v>106</v>
       </c>
       <c r="D26" t="s">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="E26" t="s">
         <v>9</v>
@@ -1851,10 +2244,10 @@
         <v>43</v>
       </c>
       <c r="C27" t="s">
-        <v>69</v>
+        <v>107</v>
       </c>
       <c r="D27" t="s">
-        <v>100</v>
+        <v>172</v>
       </c>
       <c r="E27" t="s">
         <v>9</v>
@@ -1877,7 +2270,7 @@
         <v>44</v>
       </c>
       <c r="D28" t="s">
-        <v>101</v>
+        <v>173</v>
       </c>
       <c r="E28" t="s">
         <v>9</v>
@@ -1891,22 +2284,22 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>20330051920118</v>
+        <v>20330051920368</v>
       </c>
       <c r="B29" t="s">
         <v>45</v>
       </c>
       <c r="C29" t="s">
-        <v>29</v>
+        <v>106</v>
       </c>
       <c r="D29" t="s">
-        <v>102</v>
+        <v>174</v>
       </c>
       <c r="E29" t="s">
         <v>9</v>
       </c>
       <c r="F29" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G29">
         <v>2</v>
@@ -1914,22 +2307,22 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>20330051920121</v>
+        <v>20330051920156</v>
       </c>
       <c r="B30" t="s">
         <v>46</v>
       </c>
       <c r="C30" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="D30" t="s">
-        <v>103</v>
+        <v>175</v>
       </c>
       <c r="E30" t="s">
         <v>9</v>
       </c>
       <c r="F30" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G30">
         <v>2</v>
@@ -1937,22 +2330,22 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>20330051920123</v>
+        <v>20330051920157</v>
       </c>
       <c r="B31" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="C31" t="s">
-        <v>71</v>
+        <v>108</v>
       </c>
       <c r="D31" t="s">
-        <v>104</v>
+        <v>176</v>
       </c>
       <c r="E31" t="s">
         <v>9</v>
       </c>
       <c r="F31" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G31">
         <v>2</v>
@@ -1960,22 +2353,22 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>20330051920125</v>
+        <v>20330051920369</v>
       </c>
       <c r="B32" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="C32" t="s">
-        <v>30</v>
+        <v>109</v>
       </c>
       <c r="D32" t="s">
-        <v>105</v>
+        <v>177</v>
       </c>
       <c r="E32" t="s">
         <v>9</v>
       </c>
       <c r="F32" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G32">
         <v>2</v>
@@ -1983,22 +2376,22 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>20330051920127</v>
+        <v>20330051920160</v>
       </c>
       <c r="B33" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="C33" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="D33" t="s">
-        <v>106</v>
+        <v>178</v>
       </c>
       <c r="E33" t="s">
         <v>9</v>
       </c>
       <c r="F33" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G33">
         <v>2</v>
@@ -2006,22 +2399,22 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>20330051920139</v>
+        <v>20330051920163</v>
       </c>
       <c r="B34" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="C34" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="D34" t="s">
-        <v>107</v>
+        <v>179</v>
       </c>
       <c r="E34" t="s">
         <v>9</v>
       </c>
       <c r="F34" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G34">
         <v>2</v>
@@ -2029,22 +2422,22 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>19330051920387</v>
+        <v>20330051920370</v>
       </c>
       <c r="B35" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="C35" t="s">
-        <v>28</v>
+        <v>110</v>
       </c>
       <c r="D35" t="s">
-        <v>108</v>
+        <v>180</v>
       </c>
       <c r="E35" t="s">
         <v>9</v>
       </c>
       <c r="F35" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G35">
         <v>2</v>
@@ -2052,22 +2445,22 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>20330051920389</v>
+        <v>20330051920372</v>
       </c>
       <c r="B36" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="C36" t="s">
-        <v>73</v>
+        <v>111</v>
       </c>
       <c r="D36" t="s">
-        <v>109</v>
+        <v>181</v>
       </c>
       <c r="E36" t="s">
         <v>9</v>
       </c>
       <c r="F36" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G36">
         <v>2</v>
@@ -2075,25 +2468,1422 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
+        <v>20330051920165</v>
+      </c>
+      <c r="B37" t="s">
+        <v>51</v>
+      </c>
+      <c r="C37" t="s">
+        <v>112</v>
+      </c>
+      <c r="D37" t="s">
+        <v>182</v>
+      </c>
+      <c r="E37" t="s">
+        <v>9</v>
+      </c>
+      <c r="F37" t="s">
+        <v>12</v>
+      </c>
+      <c r="G37">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38">
+        <v>20330051920167</v>
+      </c>
+      <c r="B38" t="s">
+        <v>29</v>
+      </c>
+      <c r="C38" t="s">
+        <v>113</v>
+      </c>
+      <c r="D38" t="s">
+        <v>183</v>
+      </c>
+      <c r="E38" t="s">
+        <v>9</v>
+      </c>
+      <c r="F38" t="s">
+        <v>12</v>
+      </c>
+      <c r="G38">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39">
+        <v>20330051920166</v>
+      </c>
+      <c r="B39" t="s">
+        <v>52</v>
+      </c>
+      <c r="C39" t="s">
+        <v>114</v>
+      </c>
+      <c r="D39" t="s">
+        <v>184</v>
+      </c>
+      <c r="E39" t="s">
+        <v>9</v>
+      </c>
+      <c r="F39" t="s">
+        <v>12</v>
+      </c>
+      <c r="G39">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40">
+        <v>20330051920168</v>
+      </c>
+      <c r="B40" t="s">
+        <v>53</v>
+      </c>
+      <c r="C40" t="s">
+        <v>28</v>
+      </c>
+      <c r="D40" t="s">
+        <v>185</v>
+      </c>
+      <c r="E40" t="s">
+        <v>9</v>
+      </c>
+      <c r="F40" t="s">
+        <v>12</v>
+      </c>
+      <c r="G40">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41">
+        <v>20330051920371</v>
+      </c>
+      <c r="B41" t="s">
+        <v>54</v>
+      </c>
+      <c r="C41" t="s">
+        <v>115</v>
+      </c>
+      <c r="D41" t="s">
+        <v>186</v>
+      </c>
+      <c r="E41" t="s">
+        <v>9</v>
+      </c>
+      <c r="F41" t="s">
+        <v>12</v>
+      </c>
+      <c r="G41">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42">
+        <v>20330051920171</v>
+      </c>
+      <c r="B42" t="s">
+        <v>55</v>
+      </c>
+      <c r="C42" t="s">
+        <v>116</v>
+      </c>
+      <c r="D42" t="s">
+        <v>187</v>
+      </c>
+      <c r="E42" t="s">
+        <v>9</v>
+      </c>
+      <c r="F42" t="s">
+        <v>12</v>
+      </c>
+      <c r="G42">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43">
+        <v>20330051920172</v>
+      </c>
+      <c r="B43" t="s">
+        <v>56</v>
+      </c>
+      <c r="C43" t="s">
+        <v>117</v>
+      </c>
+      <c r="D43" t="s">
+        <v>188</v>
+      </c>
+      <c r="E43" t="s">
+        <v>9</v>
+      </c>
+      <c r="F43" t="s">
+        <v>12</v>
+      </c>
+      <c r="G43">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44">
+        <v>20330051920306</v>
+      </c>
+      <c r="B44" t="s">
+        <v>57</v>
+      </c>
+      <c r="C44" t="s">
+        <v>27</v>
+      </c>
+      <c r="D44" t="s">
+        <v>189</v>
+      </c>
+      <c r="E44" t="s">
+        <v>9</v>
+      </c>
+      <c r="F44" t="s">
+        <v>12</v>
+      </c>
+      <c r="G44">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45">
+        <v>20330051920179</v>
+      </c>
+      <c r="B45" t="s">
+        <v>39</v>
+      </c>
+      <c r="C45" t="s">
+        <v>118</v>
+      </c>
+      <c r="D45" t="s">
+        <v>190</v>
+      </c>
+      <c r="E45" t="s">
+        <v>9</v>
+      </c>
+      <c r="F45" t="s">
+        <v>12</v>
+      </c>
+      <c r="G45">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46">
+        <v>20330051920180</v>
+      </c>
+      <c r="B46" t="s">
+        <v>58</v>
+      </c>
+      <c r="C46" t="s">
+        <v>89</v>
+      </c>
+      <c r="D46" t="s">
+        <v>191</v>
+      </c>
+      <c r="E46" t="s">
+        <v>9</v>
+      </c>
+      <c r="F46" t="s">
+        <v>12</v>
+      </c>
+      <c r="G46">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47">
+        <v>20330051920373</v>
+      </c>
+      <c r="B47" t="s">
+        <v>59</v>
+      </c>
+      <c r="C47" t="s">
+        <v>119</v>
+      </c>
+      <c r="D47" t="s">
+        <v>192</v>
+      </c>
+      <c r="E47" t="s">
+        <v>9</v>
+      </c>
+      <c r="F47" t="s">
+        <v>12</v>
+      </c>
+      <c r="G47">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48">
+        <v>20330051920254</v>
+      </c>
+      <c r="B48" t="s">
+        <v>41</v>
+      </c>
+      <c r="C48" t="s">
+        <v>120</v>
+      </c>
+      <c r="D48" t="s">
+        <v>193</v>
+      </c>
+      <c r="E48" t="s">
+        <v>9</v>
+      </c>
+      <c r="F48" t="s">
+        <v>12</v>
+      </c>
+      <c r="G48">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49">
+        <v>20330051920181</v>
+      </c>
+      <c r="B49" t="s">
+        <v>41</v>
+      </c>
+      <c r="C49" t="s">
+        <v>72</v>
+      </c>
+      <c r="D49" t="s">
+        <v>194</v>
+      </c>
+      <c r="E49" t="s">
+        <v>9</v>
+      </c>
+      <c r="F49" t="s">
+        <v>12</v>
+      </c>
+      <c r="G49">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50">
+        <v>20330051920182</v>
+      </c>
+      <c r="B50" t="s">
+        <v>60</v>
+      </c>
+      <c r="C50" t="s">
+        <v>121</v>
+      </c>
+      <c r="D50" t="s">
+        <v>163</v>
+      </c>
+      <c r="E50" t="s">
+        <v>9</v>
+      </c>
+      <c r="F50" t="s">
+        <v>12</v>
+      </c>
+      <c r="G50">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51">
+        <v>20330051920184</v>
+      </c>
+      <c r="B51" t="s">
+        <v>61</v>
+      </c>
+      <c r="C51" t="s">
+        <v>122</v>
+      </c>
+      <c r="D51" t="s">
+        <v>195</v>
+      </c>
+      <c r="E51" t="s">
+        <v>9</v>
+      </c>
+      <c r="F51" t="s">
+        <v>12</v>
+      </c>
+      <c r="G51">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52">
+        <v>20330051920154</v>
+      </c>
+      <c r="B52" t="s">
+        <v>62</v>
+      </c>
+      <c r="C52" t="s">
+        <v>65</v>
+      </c>
+      <c r="D52" t="s">
+        <v>196</v>
+      </c>
+      <c r="E52" t="s">
+        <v>9</v>
+      </c>
+      <c r="F52" t="s">
+        <v>12</v>
+      </c>
+      <c r="G52">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53">
+        <v>20330051920186</v>
+      </c>
+      <c r="B53" t="s">
+        <v>63</v>
+      </c>
+      <c r="C53" t="s">
+        <v>123</v>
+      </c>
+      <c r="D53" t="s">
+        <v>197</v>
+      </c>
+      <c r="E53" t="s">
+        <v>9</v>
+      </c>
+      <c r="F53" t="s">
+        <v>12</v>
+      </c>
+      <c r="G53">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54">
+        <v>20330051920388</v>
+      </c>
+      <c r="B54" t="s">
+        <v>64</v>
+      </c>
+      <c r="C54" t="s">
+        <v>124</v>
+      </c>
+      <c r="D54" t="s">
+        <v>198</v>
+      </c>
+      <c r="E54" t="s">
+        <v>9</v>
+      </c>
+      <c r="F54" t="s">
+        <v>12</v>
+      </c>
+      <c r="G54">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55">
+        <v>20330051920115</v>
+      </c>
+      <c r="B55" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" t="s">
+        <v>27</v>
+      </c>
+      <c r="D55" t="s">
+        <v>199</v>
+      </c>
+      <c r="E55" t="s">
+        <v>9</v>
+      </c>
+      <c r="F55" t="s">
+        <v>15</v>
+      </c>
+      <c r="G55">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56">
+        <v>20330051920116</v>
+      </c>
+      <c r="B56" t="s">
+        <v>65</v>
+      </c>
+      <c r="C56" t="s">
+        <v>125</v>
+      </c>
+      <c r="D56" t="s">
+        <v>200</v>
+      </c>
+      <c r="E56" t="s">
+        <v>9</v>
+      </c>
+      <c r="F56" t="s">
+        <v>15</v>
+      </c>
+      <c r="G56">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="A57">
+        <v>20330051920128</v>
+      </c>
+      <c r="B57" t="s">
+        <v>30</v>
+      </c>
+      <c r="C57" t="s">
+        <v>126</v>
+      </c>
+      <c r="D57" t="s">
+        <v>201</v>
+      </c>
+      <c r="E57" t="s">
+        <v>9</v>
+      </c>
+      <c r="F57" t="s">
+        <v>15</v>
+      </c>
+      <c r="G57">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="A58">
+        <v>20330051920131</v>
+      </c>
+      <c r="B58" t="s">
+        <v>66</v>
+      </c>
+      <c r="C58" t="s">
+        <v>48</v>
+      </c>
+      <c r="D58" t="s">
+        <v>202</v>
+      </c>
+      <c r="E58" t="s">
+        <v>9</v>
+      </c>
+      <c r="F58" t="s">
+        <v>15</v>
+      </c>
+      <c r="G58">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
+      <c r="A59">
+        <v>20330051920132</v>
+      </c>
+      <c r="B59" t="s">
+        <v>67</v>
+      </c>
+      <c r="C59" t="s">
+        <v>127</v>
+      </c>
+      <c r="D59" t="s">
+        <v>203</v>
+      </c>
+      <c r="E59" t="s">
+        <v>9</v>
+      </c>
+      <c r="F59" t="s">
+        <v>15</v>
+      </c>
+      <c r="G59">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60">
+        <v>20330051920133</v>
+      </c>
+      <c r="B60" t="s">
+        <v>67</v>
+      </c>
+      <c r="C60" t="s">
+        <v>120</v>
+      </c>
+      <c r="D60" t="s">
+        <v>204</v>
+      </c>
+      <c r="E60" t="s">
+        <v>9</v>
+      </c>
+      <c r="F60" t="s">
+        <v>15</v>
+      </c>
+      <c r="G60">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
+      <c r="A61">
+        <v>20330051920136</v>
+      </c>
+      <c r="B61" t="s">
+        <v>68</v>
+      </c>
+      <c r="C61" t="s">
+        <v>86</v>
+      </c>
+      <c r="D61" t="s">
+        <v>205</v>
+      </c>
+      <c r="E61" t="s">
+        <v>9</v>
+      </c>
+      <c r="F61" t="s">
+        <v>15</v>
+      </c>
+      <c r="G61">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
+      <c r="A62">
+        <v>20330051920137</v>
+      </c>
+      <c r="B62" t="s">
+        <v>69</v>
+      </c>
+      <c r="C62" t="s">
+        <v>128</v>
+      </c>
+      <c r="D62" t="s">
+        <v>206</v>
+      </c>
+      <c r="E62" t="s">
+        <v>9</v>
+      </c>
+      <c r="F62" t="s">
+        <v>15</v>
+      </c>
+      <c r="G62">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
+      <c r="A63">
+        <v>20330051920140</v>
+      </c>
+      <c r="B63" t="s">
+        <v>70</v>
+      </c>
+      <c r="C63" t="s">
+        <v>129</v>
+      </c>
+      <c r="D63" t="s">
+        <v>207</v>
+      </c>
+      <c r="E63" t="s">
+        <v>9</v>
+      </c>
+      <c r="F63" t="s">
+        <v>15</v>
+      </c>
+      <c r="G63">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7">
+      <c r="A64">
+        <v>20330051920141</v>
+      </c>
+      <c r="B64" t="s">
+        <v>71</v>
+      </c>
+      <c r="C64" t="s">
+        <v>130</v>
+      </c>
+      <c r="D64" t="s">
+        <v>208</v>
+      </c>
+      <c r="E64" t="s">
+        <v>9</v>
+      </c>
+      <c r="F64" t="s">
+        <v>15</v>
+      </c>
+      <c r="G64">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7">
+      <c r="A65">
+        <v>20330051920142</v>
+      </c>
+      <c r="B65" t="s">
+        <v>58</v>
+      </c>
+      <c r="C65" t="s">
+        <v>120</v>
+      </c>
+      <c r="D65" t="s">
+        <v>209</v>
+      </c>
+      <c r="E65" t="s">
+        <v>9</v>
+      </c>
+      <c r="F65" t="s">
+        <v>15</v>
+      </c>
+      <c r="G65">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7">
+      <c r="A66">
+        <v>20330051920143</v>
+      </c>
+      <c r="B66" t="s">
+        <v>72</v>
+      </c>
+      <c r="C66" t="s">
+        <v>131</v>
+      </c>
+      <c r="D66" t="s">
+        <v>210</v>
+      </c>
+      <c r="E66" t="s">
+        <v>9</v>
+      </c>
+      <c r="F66" t="s">
+        <v>15</v>
+      </c>
+      <c r="G66">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7">
+      <c r="A67">
+        <v>20330051920144</v>
+      </c>
+      <c r="B67" t="s">
+        <v>73</v>
+      </c>
+      <c r="C67" t="s">
+        <v>132</v>
+      </c>
+      <c r="D67" t="s">
+        <v>211</v>
+      </c>
+      <c r="E67" t="s">
+        <v>9</v>
+      </c>
+      <c r="F67" t="s">
+        <v>15</v>
+      </c>
+      <c r="G67">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7">
+      <c r="A68">
+        <v>20330051920153</v>
+      </c>
+      <c r="B68" t="s">
+        <v>74</v>
+      </c>
+      <c r="D68" t="s">
+        <v>212</v>
+      </c>
+      <c r="E68" t="s">
+        <v>9</v>
+      </c>
+      <c r="F68" t="s">
+        <v>15</v>
+      </c>
+      <c r="G68">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7">
+      <c r="A69">
+        <v>20330051920040</v>
+      </c>
+      <c r="B69" t="s">
+        <v>75</v>
+      </c>
+      <c r="C69" t="s">
+        <v>133</v>
+      </c>
+      <c r="D69" t="s">
+        <v>213</v>
+      </c>
+      <c r="E69" t="s">
+        <v>9</v>
+      </c>
+      <c r="F69" t="s">
+        <v>13</v>
+      </c>
+      <c r="G69">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7">
+      <c r="A70">
+        <v>20330051920045</v>
+      </c>
+      <c r="B70" t="s">
+        <v>76</v>
+      </c>
+      <c r="C70" t="s">
+        <v>125</v>
+      </c>
+      <c r="D70" t="s">
+        <v>214</v>
+      </c>
+      <c r="E70" t="s">
+        <v>9</v>
+      </c>
+      <c r="F70" t="s">
+        <v>13</v>
+      </c>
+      <c r="G70">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7">
+      <c r="A71">
+        <v>20330051920046</v>
+      </c>
+      <c r="B71" t="s">
+        <v>77</v>
+      </c>
+      <c r="C71" t="s">
+        <v>134</v>
+      </c>
+      <c r="D71" t="s">
+        <v>215</v>
+      </c>
+      <c r="E71" t="s">
+        <v>9</v>
+      </c>
+      <c r="F71" t="s">
+        <v>13</v>
+      </c>
+      <c r="G71">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7">
+      <c r="A72">
+        <v>20330051920365</v>
+      </c>
+      <c r="B72" t="s">
+        <v>78</v>
+      </c>
+      <c r="C72" t="s">
+        <v>61</v>
+      </c>
+      <c r="D72" t="s">
+        <v>216</v>
+      </c>
+      <c r="E72" t="s">
+        <v>9</v>
+      </c>
+      <c r="F72" t="s">
+        <v>13</v>
+      </c>
+      <c r="G72">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7">
+      <c r="A73">
+        <v>20330051920052</v>
+      </c>
+      <c r="B73" t="s">
+        <v>27</v>
+      </c>
+      <c r="C73" t="s">
+        <v>135</v>
+      </c>
+      <c r="D73" t="s">
+        <v>217</v>
+      </c>
+      <c r="E73" t="s">
+        <v>9</v>
+      </c>
+      <c r="F73" t="s">
+        <v>13</v>
+      </c>
+      <c r="G73">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7">
+      <c r="A74">
+        <v>20330051920056</v>
+      </c>
+      <c r="B74" t="s">
+        <v>79</v>
+      </c>
+      <c r="C74" t="s">
+        <v>129</v>
+      </c>
+      <c r="D74" t="s">
+        <v>218</v>
+      </c>
+      <c r="E74" t="s">
+        <v>9</v>
+      </c>
+      <c r="F74" t="s">
+        <v>13</v>
+      </c>
+      <c r="G74">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7">
+      <c r="A75">
+        <v>20330051920099</v>
+      </c>
+      <c r="B75" t="s">
+        <v>80</v>
+      </c>
+      <c r="D75" t="s">
+        <v>219</v>
+      </c>
+      <c r="E75" t="s">
+        <v>9</v>
+      </c>
+      <c r="F75" t="s">
+        <v>13</v>
+      </c>
+      <c r="G75">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7">
+      <c r="A76">
+        <v>20330051920101</v>
+      </c>
+      <c r="B76" t="s">
+        <v>81</v>
+      </c>
+      <c r="C76" t="s">
+        <v>136</v>
+      </c>
+      <c r="D76" t="s">
+        <v>220</v>
+      </c>
+      <c r="E76" t="s">
+        <v>9</v>
+      </c>
+      <c r="F76" t="s">
+        <v>13</v>
+      </c>
+      <c r="G76">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7">
+      <c r="A77">
+        <v>20330051920107</v>
+      </c>
+      <c r="B77" t="s">
+        <v>41</v>
+      </c>
+      <c r="C77" t="s">
+        <v>41</v>
+      </c>
+      <c r="D77" t="s">
+        <v>221</v>
+      </c>
+      <c r="E77" t="s">
+        <v>9</v>
+      </c>
+      <c r="F77" t="s">
+        <v>13</v>
+      </c>
+      <c r="G77">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7">
+      <c r="A78">
+        <v>20330051920109</v>
+      </c>
+      <c r="B78" t="s">
+        <v>82</v>
+      </c>
+      <c r="C78" t="s">
+        <v>134</v>
+      </c>
+      <c r="D78" t="s">
+        <v>222</v>
+      </c>
+      <c r="E78" t="s">
+        <v>9</v>
+      </c>
+      <c r="F78" t="s">
+        <v>13</v>
+      </c>
+      <c r="G78">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7">
+      <c r="A79">
+        <v>20330051920112</v>
+      </c>
+      <c r="B79" t="s">
+        <v>83</v>
+      </c>
+      <c r="C79" t="s">
+        <v>104</v>
+      </c>
+      <c r="D79" t="s">
+        <v>223</v>
+      </c>
+      <c r="E79" t="s">
+        <v>9</v>
+      </c>
+      <c r="F79" t="s">
+        <v>13</v>
+      </c>
+      <c r="G79">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7">
+      <c r="A80">
+        <v>20330051920118</v>
+      </c>
+      <c r="B80" t="s">
+        <v>84</v>
+      </c>
+      <c r="C80" t="s">
+        <v>29</v>
+      </c>
+      <c r="D80" t="s">
+        <v>224</v>
+      </c>
+      <c r="E80" t="s">
+        <v>9</v>
+      </c>
+      <c r="F80" t="s">
+        <v>15</v>
+      </c>
+      <c r="G80">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7">
+      <c r="A81">
+        <v>20330051920121</v>
+      </c>
+      <c r="B81" t="s">
+        <v>85</v>
+      </c>
+      <c r="C81" t="s">
+        <v>137</v>
+      </c>
+      <c r="D81" t="s">
+        <v>225</v>
+      </c>
+      <c r="E81" t="s">
+        <v>9</v>
+      </c>
+      <c r="F81" t="s">
+        <v>15</v>
+      </c>
+      <c r="G81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7">
+      <c r="A82">
+        <v>20330051920123</v>
+      </c>
+      <c r="B82" t="s">
+        <v>28</v>
+      </c>
+      <c r="C82" t="s">
+        <v>138</v>
+      </c>
+      <c r="D82" t="s">
+        <v>226</v>
+      </c>
+      <c r="E82" t="s">
+        <v>9</v>
+      </c>
+      <c r="F82" t="s">
+        <v>15</v>
+      </c>
+      <c r="G82">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7">
+      <c r="A83">
+        <v>20330051920125</v>
+      </c>
+      <c r="B83" t="s">
+        <v>29</v>
+      </c>
+      <c r="C83" t="s">
+        <v>30</v>
+      </c>
+      <c r="D83" t="s">
+        <v>227</v>
+      </c>
+      <c r="E83" t="s">
+        <v>9</v>
+      </c>
+      <c r="F83" t="s">
+        <v>15</v>
+      </c>
+      <c r="G83">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7">
+      <c r="A84">
+        <v>20330051920127</v>
+      </c>
+      <c r="B84" t="s">
+        <v>30</v>
+      </c>
+      <c r="C84" t="s">
+        <v>30</v>
+      </c>
+      <c r="D84" t="s">
+        <v>228</v>
+      </c>
+      <c r="E84" t="s">
+        <v>9</v>
+      </c>
+      <c r="F84" t="s">
+        <v>15</v>
+      </c>
+      <c r="G84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7">
+      <c r="A85">
+        <v>20330051920139</v>
+      </c>
+      <c r="B85" t="s">
+        <v>86</v>
+      </c>
+      <c r="C85" t="s">
+        <v>139</v>
+      </c>
+      <c r="D85" t="s">
+        <v>229</v>
+      </c>
+      <c r="E85" t="s">
+        <v>9</v>
+      </c>
+      <c r="F85" t="s">
+        <v>15</v>
+      </c>
+      <c r="G85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7">
+      <c r="A86">
+        <v>19330051920387</v>
+      </c>
+      <c r="B86" t="s">
+        <v>37</v>
+      </c>
+      <c r="C86" t="s">
+        <v>28</v>
+      </c>
+      <c r="D86" t="s">
+        <v>230</v>
+      </c>
+      <c r="E86" t="s">
+        <v>9</v>
+      </c>
+      <c r="F86" t="s">
+        <v>15</v>
+      </c>
+      <c r="G86">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7">
+      <c r="A87">
+        <v>20330051920389</v>
+      </c>
+      <c r="B87" t="s">
+        <v>87</v>
+      </c>
+      <c r="C87" t="s">
+        <v>140</v>
+      </c>
+      <c r="D87" t="s">
+        <v>231</v>
+      </c>
+      <c r="E87" t="s">
+        <v>9</v>
+      </c>
+      <c r="F87" t="s">
+        <v>15</v>
+      </c>
+      <c r="G87">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7">
+      <c r="A88">
         <v>20330051920150</v>
       </c>
-      <c r="B37" t="s">
-        <v>49</v>
-      </c>
-      <c r="C37" t="s">
-        <v>74</v>
-      </c>
-      <c r="D37" t="s">
-        <v>110</v>
-      </c>
-      <c r="E37" t="s">
-        <v>9</v>
-      </c>
-      <c r="F37" t="s">
+      <c r="B88" t="s">
+        <v>88</v>
+      </c>
+      <c r="C88" t="s">
+        <v>141</v>
+      </c>
+      <c r="D88" t="s">
+        <v>232</v>
+      </c>
+      <c r="E88" t="s">
+        <v>9</v>
+      </c>
+      <c r="F88" t="s">
         <v>15</v>
       </c>
-      <c r="G37">
-        <v>2</v>
+      <c r="G88">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7">
+      <c r="A89">
+        <v>20330051920043</v>
+      </c>
+      <c r="B89" t="s">
+        <v>89</v>
+      </c>
+      <c r="C89" t="s">
+        <v>142</v>
+      </c>
+      <c r="D89" t="s">
+        <v>233</v>
+      </c>
+      <c r="E89" t="s">
+        <v>9</v>
+      </c>
+      <c r="F89" t="s">
+        <v>13</v>
+      </c>
+      <c r="G89">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7">
+      <c r="A90">
+        <v>20330051920048</v>
+      </c>
+      <c r="B90" t="s">
+        <v>25</v>
+      </c>
+      <c r="C90" t="s">
+        <v>29</v>
+      </c>
+      <c r="D90" t="s">
+        <v>234</v>
+      </c>
+      <c r="E90" t="s">
+        <v>9</v>
+      </c>
+      <c r="F90" t="s">
+        <v>13</v>
+      </c>
+      <c r="G90">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7">
+      <c r="A91">
+        <v>20330051920050</v>
+      </c>
+      <c r="B91" t="s">
+        <v>90</v>
+      </c>
+      <c r="C91" t="s">
+        <v>143</v>
+      </c>
+      <c r="D91" t="s">
+        <v>235</v>
+      </c>
+      <c r="E91" t="s">
+        <v>9</v>
+      </c>
+      <c r="F91" t="s">
+        <v>13</v>
+      </c>
+      <c r="G91">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7">
+      <c r="A92">
+        <v>20330051920051</v>
+      </c>
+      <c r="B92" t="s">
+        <v>26</v>
+      </c>
+      <c r="C92" t="s">
+        <v>144</v>
+      </c>
+      <c r="D92" t="s">
+        <v>215</v>
+      </c>
+      <c r="E92" t="s">
+        <v>9</v>
+      </c>
+      <c r="F92" t="s">
+        <v>13</v>
+      </c>
+      <c r="G92">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7">
+      <c r="A93">
+        <v>20330051920053</v>
+      </c>
+      <c r="B93" t="s">
+        <v>28</v>
+      </c>
+      <c r="C93" t="s">
+        <v>35</v>
+      </c>
+      <c r="D93" t="s">
+        <v>236</v>
+      </c>
+      <c r="E93" t="s">
+        <v>9</v>
+      </c>
+      <c r="F93" t="s">
+        <v>13</v>
+      </c>
+      <c r="G93">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7">
+      <c r="A94">
+        <v>20330051920057</v>
+      </c>
+      <c r="B94" t="s">
+        <v>29</v>
+      </c>
+      <c r="C94" t="s">
+        <v>145</v>
+      </c>
+      <c r="D94" t="s">
+        <v>237</v>
+      </c>
+      <c r="E94" t="s">
+        <v>9</v>
+      </c>
+      <c r="F94" t="s">
+        <v>13</v>
+      </c>
+      <c r="G94">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7">
+      <c r="A95">
+        <v>20330051920095</v>
+      </c>
+      <c r="B95" t="s">
+        <v>91</v>
+      </c>
+      <c r="C95" t="s">
+        <v>79</v>
+      </c>
+      <c r="D95" t="s">
+        <v>238</v>
+      </c>
+      <c r="E95" t="s">
+        <v>9</v>
+      </c>
+      <c r="F95" t="s">
+        <v>13</v>
+      </c>
+      <c r="G95">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7">
+      <c r="A96">
+        <v>20330051920058</v>
+      </c>
+      <c r="B96" t="s">
+        <v>92</v>
+      </c>
+      <c r="C96" t="s">
+        <v>146</v>
+      </c>
+      <c r="D96" t="s">
+        <v>239</v>
+      </c>
+      <c r="E96" t="s">
+        <v>9</v>
+      </c>
+      <c r="F96" t="s">
+        <v>13</v>
+      </c>
+      <c r="G96">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7">
+      <c r="A97">
+        <v>20330051920104</v>
+      </c>
+      <c r="B97" t="s">
+        <v>92</v>
+      </c>
+      <c r="C97" t="s">
+        <v>35</v>
+      </c>
+      <c r="D97" t="s">
+        <v>240</v>
+      </c>
+      <c r="E97" t="s">
+        <v>9</v>
+      </c>
+      <c r="F97" t="s">
+        <v>13</v>
+      </c>
+      <c r="G97">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7">
+      <c r="A98">
+        <v>20330051920105</v>
+      </c>
+      <c r="B98" t="s">
+        <v>72</v>
+      </c>
+      <c r="C98" t="s">
+        <v>30</v>
+      </c>
+      <c r="D98" t="s">
+        <v>241</v>
+      </c>
+      <c r="E98" t="s">
+        <v>9</v>
+      </c>
+      <c r="F98" t="s">
+        <v>13</v>
+      </c>
+      <c r="G98">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/González Sánchez Rene Aurelio - Estadisticos 20212.xlsx
+++ b/docentes/González Sánchez Rene Aurelio - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="105">
   <si>
     <t>Mat</t>
   </si>
@@ -112,63 +112,66 @@
     <t>MAZAHUA</t>
   </si>
   <si>
+    <t>MAYAHUA</t>
+  </si>
+  <si>
+    <t>OSORIO</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>MENDIZABAL</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>LARRINAGA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>PLIEGO</t>
+  </si>
+  <si>
+    <t>ARROYO</t>
+  </si>
+  <si>
+    <t>MATA</t>
+  </si>
+  <si>
+    <t>PARRA</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>ZUÑIGA</t>
+  </si>
+  <si>
     <t>CASTELLANOS</t>
   </si>
   <si>
-    <t>MAYAHUA</t>
-  </si>
-  <si>
-    <t>OSORIO</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>MENDIZABAL</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>LARRINAGA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>PLIEGO</t>
-  </si>
-  <si>
-    <t>ARROYO</t>
-  </si>
-  <si>
-    <t>MATA</t>
-  </si>
-  <si>
-    <t>PARRA</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>ZUÑIGA</t>
-  </si>
-  <si>
     <t>CID</t>
   </si>
   <si>
@@ -193,6 +196,9 @@
     <t>MACHORRO</t>
   </si>
   <si>
+    <t>SALAZAR</t>
+  </si>
+  <si>
     <t>SEGURA</t>
   </si>
   <si>
@@ -262,64 +268,67 @@
     <t>GENARO RAFAEL</t>
   </si>
   <si>
+    <t>DAMARIS</t>
+  </si>
+  <si>
+    <t>KARLA</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>CESAR</t>
+  </si>
+  <si>
+    <t>ALDER ALBERTO</t>
+  </si>
+  <si>
+    <t>NAHOMI ITZAYANA</t>
+  </si>
+  <si>
+    <t>YAIR DAVID</t>
+  </si>
+  <si>
+    <t>CRISTIAN JAHIR</t>
+  </si>
+  <si>
+    <t>SAID ANDRES</t>
+  </si>
+  <si>
+    <t>JOHAN ALEJANDRO</t>
+  </si>
+  <si>
+    <t>AMANDA MICHEL</t>
+  </si>
+  <si>
+    <t>VICTOR GAEL</t>
+  </si>
+  <si>
+    <t>JORGE ALEJANDRO</t>
+  </si>
+  <si>
+    <t>GONZALO FEDERICO</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>VICTOR GAMALIEL</t>
+  </si>
+  <si>
+    <t>VICTOR HUGO</t>
+  </si>
+  <si>
+    <t>CRISTIAN ARTURO</t>
+  </si>
+  <si>
+    <t>SUEMI</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
     <t>MELANIE NAOMI</t>
-  </si>
-  <si>
-    <t>DAMARIS</t>
-  </si>
-  <si>
-    <t>KARLA</t>
-  </si>
-  <si>
-    <t>CESAR</t>
-  </si>
-  <si>
-    <t>ALDER ALBERTO</t>
-  </si>
-  <si>
-    <t>NAHOMI ITZAYANA</t>
-  </si>
-  <si>
-    <t>YAIR DAVID</t>
-  </si>
-  <si>
-    <t>CRISTIAN JAHIR</t>
-  </si>
-  <si>
-    <t>SAID ANDRES</t>
-  </si>
-  <si>
-    <t>JOHAN ALEJANDRO</t>
-  </si>
-  <si>
-    <t>AMANDA MICHEL</t>
-  </si>
-  <si>
-    <t>VICTOR GAEL</t>
-  </si>
-  <si>
-    <t>JORGE ALEJANDRO</t>
-  </si>
-  <si>
-    <t>GONZALO FEDERICO</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>VICTOR GAMALIEL</t>
-  </si>
-  <si>
-    <t>VICTOR HUGO</t>
-  </si>
-  <si>
-    <t>CRISTIAN ARTURO</t>
-  </si>
-  <si>
-    <t>SUEMI</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
   </si>
   <si>
     <t>JESUS</t>
@@ -1247,7 +1256,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1285,10 +1294,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1308,10 +1317,10 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1331,10 +1340,10 @@
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -1357,7 +1366,7 @@
         <v>22</v>
       </c>
       <c r="D5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -1380,7 +1389,7 @@
         <v>36</v>
       </c>
       <c r="D6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -1400,10 +1409,10 @@
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -1426,7 +1435,7 @@
         <v>38</v>
       </c>
       <c r="D8" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -1446,10 +1455,10 @@
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D9" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -1469,10 +1478,10 @@
         <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -1486,16 +1495,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920115</v>
+        <v>20330051920137</v>
       </c>
       <c r="B11" t="s">
         <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="D11" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -1509,16 +1518,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920137</v>
+        <v>20330051920141</v>
       </c>
       <c r="B12" t="s">
         <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D12" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
@@ -1532,16 +1541,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920141</v>
+        <v>20330051920387</v>
       </c>
       <c r="B13" t="s">
         <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D13" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
@@ -1561,10 +1570,10 @@
         <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
@@ -1584,7 +1593,7 @@
         <v>35</v>
       </c>
       <c r="D15" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
@@ -1604,10 +1613,10 @@
         <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D16" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1627,10 +1636,10 @@
         <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D17" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1650,10 +1659,10 @@
         <v>38</v>
       </c>
       <c r="C18" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D18" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E18" t="s">
         <v>9</v>
@@ -1673,10 +1682,10 @@
         <v>38</v>
       </c>
       <c r="C19" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D19" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E19" t="s">
         <v>9</v>
@@ -1696,10 +1705,10 @@
         <v>23</v>
       </c>
       <c r="C20" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D20" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E20" t="s">
         <v>9</v>
@@ -1719,10 +1728,10 @@
         <v>39</v>
       </c>
       <c r="C21" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D21" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E21" t="s">
         <v>9</v>
@@ -1742,10 +1751,10 @@
         <v>40</v>
       </c>
       <c r="C22" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D22" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E22" t="s">
         <v>9</v>
@@ -1765,10 +1774,10 @@
         <v>41</v>
       </c>
       <c r="C23" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D23" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E23" t="s">
         <v>9</v>
@@ -1788,10 +1797,10 @@
         <v>42</v>
       </c>
       <c r="C24" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D24" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E24" t="s">
         <v>9</v>
@@ -1811,10 +1820,10 @@
         <v>43</v>
       </c>
       <c r="C25" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D25" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E25" t="s">
         <v>9</v>
@@ -1834,10 +1843,10 @@
         <v>44</v>
       </c>
       <c r="C26" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D26" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E26" t="s">
         <v>9</v>
@@ -1857,10 +1866,10 @@
         <v>45</v>
       </c>
       <c r="C27" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D27" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E27" t="s">
         <v>9</v>
@@ -1880,10 +1889,10 @@
         <v>46</v>
       </c>
       <c r="C28" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D28" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E28" t="s">
         <v>9</v>
@@ -1906,7 +1915,7 @@
         <v>34</v>
       </c>
       <c r="D29" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E29" t="s">
         <v>9</v>
@@ -1926,10 +1935,10 @@
         <v>48</v>
       </c>
       <c r="C30" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D30" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E30" t="s">
         <v>9</v>
@@ -1949,10 +1958,10 @@
         <v>49</v>
       </c>
       <c r="C31" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D31" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E31" t="s">
         <v>9</v>
@@ -1966,24 +1975,47 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>20330051920046</v>
+        <v>20330051920115</v>
       </c>
       <c r="B32" t="s">
         <v>50</v>
       </c>
       <c r="C32" t="s">
-        <v>71</v>
+        <v>34</v>
       </c>
       <c r="D32" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E32" t="s">
         <v>9</v>
       </c>
       <c r="F32" t="s">
+        <v>15</v>
+      </c>
+      <c r="G32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33">
+        <v>20330051920046</v>
+      </c>
+      <c r="B33" t="s">
+        <v>51</v>
+      </c>
+      <c r="C33" t="s">
+        <v>73</v>
+      </c>
+      <c r="D33" t="s">
+        <v>104</v>
+      </c>
+      <c r="E33" t="s">
+        <v>9</v>
+      </c>
+      <c r="F33" t="s">
         <v>13</v>
       </c>
-      <c r="G32">
+      <c r="G33">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Sánchez Rene Aurelio - Estadisticos 20212.xlsx
+++ b/docentes/González Sánchez Rene Aurelio - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="109">
   <si>
     <t>Mat</t>
   </si>
@@ -85,210 +85,228 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>MARROQUIN</t>
+  </si>
+  <si>
+    <t>OLMOS</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>SILVESTRE</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
+    <t>ARROYO</t>
+  </si>
+  <si>
+    <t>ZUÑIGA</t>
+  </si>
+  <si>
+    <t>MAYAHUA</t>
+  </si>
+  <si>
+    <t>OSORIO</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>MENDIZABAL</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
     <t>PEREZ</t>
   </si>
   <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>MARROQUIN</t>
-  </si>
-  <si>
-    <t>OLMOS</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>MAYAHUA</t>
-  </si>
-  <si>
-    <t>OSORIO</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>LARRINAGA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>PLIEGO</t>
+  </si>
+  <si>
+    <t>MATA</t>
+  </si>
+  <si>
+    <t>PARRA</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>CASTELLANOS</t>
+  </si>
+  <si>
+    <t>CID</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>URBINA</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>ACEVEDO</t>
+  </si>
+  <si>
+    <t>MONTALVO</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>XOCHIQUISQUI</t>
+  </si>
+  <si>
+    <t>MACHORRO</t>
+  </si>
+  <si>
+    <t>SALAZAR</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>VELASCO</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>ALAMILLO</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>SALAS</t>
+  </si>
+  <si>
+    <t>SANTES</t>
+  </si>
+  <si>
+    <t>LORENZO</t>
+  </si>
+  <si>
+    <t>CANSECO</t>
   </si>
   <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>MENDIZABAL</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>LARRINAGA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>PLIEGO</t>
-  </si>
-  <si>
-    <t>ARROYO</t>
-  </si>
-  <si>
-    <t>MATA</t>
-  </si>
-  <si>
-    <t>PARRA</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>ZUÑIGA</t>
-  </si>
-  <si>
-    <t>CASTELLANOS</t>
-  </si>
-  <si>
-    <t>CID</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>VELASCO</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>URBINA</t>
-  </si>
-  <si>
-    <t>ACEVEDO</t>
-  </si>
-  <si>
-    <t>XOCHIQUISQUI</t>
-  </si>
-  <si>
-    <t>MACHORRO</t>
-  </si>
-  <si>
-    <t>SALAZAR</t>
-  </si>
-  <si>
-    <t>SEGURA</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>ALAMILLO</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>SALAS</t>
-  </si>
-  <si>
-    <t>SANTES</t>
-  </si>
-  <si>
-    <t>LORENZO</t>
-  </si>
-  <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>CANSECO</t>
-  </si>
-  <si>
     <t>MELO</t>
   </si>
   <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
     <t>VALENCIA</t>
   </si>
   <si>
+    <t>JESUS ISRAEL</t>
+  </si>
+  <si>
+    <t>GABRIEL JOSUE</t>
+  </si>
+  <si>
+    <t>ANGEL</t>
+  </si>
+  <si>
+    <t>ALDIR ADALBERTO</t>
+  </si>
+  <si>
+    <t>YAIR</t>
+  </si>
+  <si>
+    <t>JONATHAN</t>
+  </si>
+  <si>
+    <t>AYLIN MELISSA</t>
+  </si>
+  <si>
+    <t>GENARO RAFAEL</t>
+  </si>
+  <si>
+    <t>VICTOR HUGO</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
+    <t>DAMARIS</t>
+  </si>
+  <si>
+    <t>KARLA</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>ALDER ALBERTO</t>
+  </si>
+  <si>
+    <t>JOSUE EDUARDO</t>
+  </si>
+  <si>
+    <t>NAHOMI ITZAYANA</t>
+  </si>
+  <si>
+    <t>YAIR DAVID</t>
+  </si>
+  <si>
     <t>CRISTIAN MANUEL</t>
   </si>
   <si>
+    <t>ANGEL DE JESUS</t>
+  </si>
+  <si>
     <t>LUZ AMELY</t>
   </si>
   <si>
-    <t>JESUS ISRAEL</t>
-  </si>
-  <si>
-    <t>GABRIEL JOSUE</t>
-  </si>
-  <si>
-    <t>ANGEL</t>
-  </si>
-  <si>
-    <t>ALDIR ADALBERTO</t>
-  </si>
-  <si>
-    <t>JONATHAN</t>
-  </si>
-  <si>
-    <t>AYLIN MELISSA</t>
-  </si>
-  <si>
-    <t>GENARO RAFAEL</t>
-  </si>
-  <si>
-    <t>DAMARIS</t>
-  </si>
-  <si>
-    <t>KARLA</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>CESAR</t>
-  </si>
-  <si>
-    <t>ALDER ALBERTO</t>
-  </si>
-  <si>
-    <t>NAHOMI ITZAYANA</t>
-  </si>
-  <si>
-    <t>YAIR DAVID</t>
-  </si>
-  <si>
     <t>CRISTIAN JAHIR</t>
   </si>
   <si>
@@ -316,16 +334,10 @@
     <t>VICTOR GAMALIEL</t>
   </si>
   <si>
-    <t>VICTOR HUGO</t>
-  </si>
-  <si>
     <t>CRISTIAN ARTURO</t>
   </si>
   <si>
     <t>SUEMI</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
   </si>
   <si>
     <t>MELANIE NAOMI</t>
@@ -755,10 +767,10 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -767,7 +779,7 @@
         <v>30</v>
       </c>
       <c r="G3">
-        <v>81.08</v>
+        <v>83.33</v>
       </c>
       <c r="H3">
         <v>8.300000000000001</v>
@@ -947,10 +959,10 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D3">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E3">
         <v>30</v>
@@ -1127,10 +1139,10 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -1139,7 +1151,7 @@
         <v>30</v>
       </c>
       <c r="G3">
-        <v>81.08</v>
+        <v>83.33</v>
       </c>
       <c r="H3">
         <v>8.300000000000001</v>
@@ -1256,7 +1268,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1288,22 +1300,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920341</v>
+        <v>19330051920051</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1311,22 +1323,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920348</v>
+        <v>20330051920087</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1334,16 +1346,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920051</v>
+        <v>20330051920091</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="D4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -1357,16 +1369,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920087</v>
+        <v>20330051920065</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="D5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -1380,16 +1392,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920091</v>
+        <v>20330051920066</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="D6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -1403,16 +1415,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920065</v>
+        <v>20330051920068</v>
       </c>
       <c r="B7" t="s">
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="D7" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -1426,16 +1438,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920068</v>
+        <v>20330051920069</v>
       </c>
       <c r="B8" t="s">
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="D8" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -1449,22 +1461,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920069</v>
+        <v>20330051920236</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D9" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1472,22 +1484,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920236</v>
+        <v>20330051920157</v>
       </c>
       <c r="B10" t="s">
         <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1495,22 +1507,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920137</v>
+        <v>20330051920388</v>
       </c>
       <c r="B11" t="s">
         <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D11" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1518,16 +1530,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920141</v>
+        <v>20330051920137</v>
       </c>
       <c r="B12" t="s">
         <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
@@ -1541,16 +1553,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920387</v>
+        <v>20330051920141</v>
       </c>
       <c r="B13" t="s">
         <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
@@ -1564,22 +1576,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920052</v>
+        <v>20330051920387</v>
       </c>
       <c r="B14" t="s">
         <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D14" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
       </c>
       <c r="F14" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G14">
         <v>2</v>
@@ -1593,7 +1605,7 @@
         <v>35</v>
       </c>
       <c r="D15" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
@@ -1607,16 +1619,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920335</v>
+        <v>21330051920334</v>
       </c>
       <c r="B16" t="s">
         <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="D16" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1630,16 +1642,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920336</v>
+        <v>21330051920335</v>
       </c>
       <c r="B17" t="s">
         <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D17" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1653,22 +1665,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>20330051920081</v>
+        <v>21330051920336</v>
       </c>
       <c r="B18" t="s">
         <v>38</v>
       </c>
       <c r="C18" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D18" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E18" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1676,22 +1688,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>20330051920082</v>
+        <v>21330051920341</v>
       </c>
       <c r="B19" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C19" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D19" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -1699,22 +1711,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>20330051920093</v>
+        <v>21330051920347</v>
       </c>
       <c r="B20" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="C20" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D20" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E20" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -1722,22 +1734,22 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>20330051920062</v>
+        <v>21330051920348</v>
       </c>
       <c r="B21" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C21" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D21" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E21" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F21" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -1745,16 +1757,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>20330051920063</v>
+        <v>20330051920081</v>
       </c>
       <c r="B22" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C22" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D22" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E22" t="s">
         <v>9</v>
@@ -1768,16 +1780,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>20330051920064</v>
+        <v>20330051920082</v>
       </c>
       <c r="B23" t="s">
         <v>41</v>
       </c>
       <c r="C23" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="D23" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E23" t="s">
         <v>9</v>
@@ -1791,22 +1803,22 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>20330051920234</v>
+        <v>20330051920093</v>
       </c>
       <c r="B24" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C24" t="s">
         <v>67</v>
       </c>
       <c r="D24" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E24" t="s">
         <v>9</v>
       </c>
       <c r="F24" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1814,22 +1826,22 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>20330051920240</v>
+        <v>20330051920062</v>
       </c>
       <c r="B25" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C25" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D25" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E25" t="s">
         <v>9</v>
       </c>
       <c r="F25" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -1837,22 +1849,22 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>20330051920244</v>
+        <v>20330051920063</v>
       </c>
       <c r="B26" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C26" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D26" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E26" t="s">
         <v>9</v>
       </c>
       <c r="F26" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -1860,22 +1872,22 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>20330051920157</v>
+        <v>20330051920064</v>
       </c>
       <c r="B27" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C27" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D27" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E27" t="s">
         <v>9</v>
       </c>
       <c r="F27" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -1883,22 +1895,22 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>20330051920172</v>
+        <v>20330051920234</v>
       </c>
       <c r="B28" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C28" t="s">
         <v>70</v>
       </c>
       <c r="D28" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E28" t="s">
         <v>9</v>
       </c>
       <c r="F28" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G28">
         <v>1</v>
@@ -1906,22 +1918,22 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>20330051920306</v>
+        <v>20330051920240</v>
       </c>
       <c r="B29" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C29" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="D29" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E29" t="s">
         <v>9</v>
       </c>
       <c r="F29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -1929,22 +1941,22 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>20330051920182</v>
+        <v>20330051920244</v>
       </c>
       <c r="B30" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C30" t="s">
         <v>71</v>
       </c>
       <c r="D30" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="E30" t="s">
         <v>9</v>
       </c>
       <c r="F30" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G30">
         <v>1</v>
@@ -1952,16 +1964,16 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>20330051920388</v>
+        <v>20330051920172</v>
       </c>
       <c r="B31" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C31" t="s">
         <v>72</v>
       </c>
       <c r="D31" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E31" t="s">
         <v>9</v>
@@ -1975,22 +1987,22 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>20330051920115</v>
+        <v>20330051920306</v>
       </c>
       <c r="B32" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C32" t="s">
-        <v>34</v>
+        <v>73</v>
       </c>
       <c r="D32" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E32" t="s">
         <v>9</v>
       </c>
       <c r="F32" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G32">
         <v>1</v>
@@ -1998,24 +2010,70 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
+        <v>20330051920182</v>
+      </c>
+      <c r="B33" t="s">
+        <v>50</v>
+      </c>
+      <c r="C33" t="s">
+        <v>74</v>
+      </c>
+      <c r="D33" t="s">
+        <v>103</v>
+      </c>
+      <c r="E33" t="s">
+        <v>9</v>
+      </c>
+      <c r="F33" t="s">
+        <v>12</v>
+      </c>
+      <c r="G33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34">
+        <v>20330051920115</v>
+      </c>
+      <c r="B34" t="s">
+        <v>51</v>
+      </c>
+      <c r="C34" t="s">
+        <v>73</v>
+      </c>
+      <c r="D34" t="s">
+        <v>107</v>
+      </c>
+      <c r="E34" t="s">
+        <v>9</v>
+      </c>
+      <c r="F34" t="s">
+        <v>15</v>
+      </c>
+      <c r="G34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35">
         <v>20330051920046</v>
       </c>
-      <c r="B33" t="s">
-        <v>51</v>
-      </c>
-      <c r="C33" t="s">
-        <v>73</v>
-      </c>
-      <c r="D33" t="s">
-        <v>104</v>
-      </c>
-      <c r="E33" t="s">
-        <v>9</v>
-      </c>
-      <c r="F33" t="s">
+      <c r="B35" t="s">
+        <v>52</v>
+      </c>
+      <c r="C35" t="s">
+        <v>75</v>
+      </c>
+      <c r="D35" t="s">
+        <v>108</v>
+      </c>
+      <c r="E35" t="s">
+        <v>9</v>
+      </c>
+      <c r="F35" t="s">
         <v>13</v>
       </c>
-      <c r="G33">
+      <c r="G35">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Sánchez Rene Aurelio - Estadisticos 20212.xlsx
+++ b/docentes/González Sánchez Rene Aurelio - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="77">
   <si>
     <t>Mat</t>
   </si>
@@ -85,265 +85,169 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>MARROQUIN</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>SILVESTRE</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>OSORIO</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>MENDIZABAL</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
-    <t>MARROQUIN</t>
-  </si>
-  <si>
-    <t>OLMOS</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>SILVESTRE</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>ARROYO</t>
-  </si>
-  <si>
-    <t>ZUÑIGA</t>
-  </si>
-  <si>
-    <t>MAYAHUA</t>
-  </si>
-  <si>
-    <t>OSORIO</t>
+    <t>ROSETE</t>
+  </si>
+  <si>
+    <t>LARRINAGA</t>
   </si>
   <si>
     <t>ROSAS</t>
   </si>
   <si>
-    <t>MENDIZABAL</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>URBINA</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
   </si>
   <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>LARRINAGA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>PLIEGO</t>
-  </si>
-  <si>
-    <t>MATA</t>
-  </si>
-  <si>
-    <t>PARRA</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>CASTELLANOS</t>
-  </si>
-  <si>
-    <t>CID</t>
+    <t>NOYOLA</t>
+  </si>
+  <si>
+    <t>MACHORRO</t>
+  </si>
+  <si>
+    <t>RAMON</t>
+  </si>
+  <si>
+    <t>CONCHE</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>CORONA</t>
   </si>
   <si>
     <t>CRUZ</t>
   </si>
   <si>
-    <t>URBINA</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>ACEVEDO</t>
-  </si>
-  <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>XOCHIQUISQUI</t>
-  </si>
-  <si>
-    <t>MACHORRO</t>
+    <t>SALAS</t>
+  </si>
+  <si>
+    <t>SANTES</t>
   </si>
   <si>
     <t>SALAZAR</t>
   </si>
   <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>VELASCO</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>ALAMILLO</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>SALAS</t>
-  </si>
-  <si>
-    <t>SANTES</t>
-  </si>
-  <si>
-    <t>LORENZO</t>
-  </si>
-  <si>
-    <t>CANSECO</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>MELO</t>
-  </si>
-  <si>
-    <t>VALENCIA</t>
+    <t>GABRIEL JOSUE</t>
+  </si>
+  <si>
+    <t>ALAN URIEL</t>
+  </si>
+  <si>
+    <t>ALDIR ADALBERTO</t>
+  </si>
+  <si>
+    <t>YAIR</t>
+  </si>
+  <si>
+    <t>VANNIA GISELLE</t>
+  </si>
+  <si>
+    <t>ESMERALDA</t>
+  </si>
+  <si>
+    <t>MARIA JOSE</t>
+  </si>
+  <si>
+    <t>KARLA</t>
+  </si>
+  <si>
+    <t>XIMENA MICHELL</t>
+  </si>
+  <si>
+    <t>MEILYN ADABEL</t>
+  </si>
+  <si>
+    <t>GUSTAVO</t>
+  </si>
+  <si>
+    <t>ALDER ALBERTO</t>
+  </si>
+  <si>
+    <t>NAHOMI ITZAYANA</t>
+  </si>
+  <si>
+    <t>GAEL JARED</t>
+  </si>
+  <si>
+    <t>ANGEL DE JESUS</t>
+  </si>
+  <si>
+    <t>ABIGAIL</t>
   </si>
   <si>
     <t>JESUS ISRAEL</t>
   </si>
   <si>
-    <t>GABRIEL JOSUE</t>
-  </si>
-  <si>
-    <t>ANGEL</t>
-  </si>
-  <si>
-    <t>ALDIR ADALBERTO</t>
-  </si>
-  <si>
-    <t>YAIR</t>
-  </si>
-  <si>
-    <t>JONATHAN</t>
-  </si>
-  <si>
-    <t>AYLIN MELISSA</t>
-  </si>
-  <si>
-    <t>GENARO RAFAEL</t>
-  </si>
-  <si>
-    <t>VICTOR HUGO</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
-  </si>
-  <si>
-    <t>DAMARIS</t>
-  </si>
-  <si>
-    <t>KARLA</t>
+    <t>VICTOR GAEL</t>
+  </si>
+  <si>
+    <t>GONZALO FEDERICO</t>
   </si>
   <si>
     <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>ALDER ALBERTO</t>
-  </si>
-  <si>
-    <t>JOSUE EDUARDO</t>
-  </si>
-  <si>
-    <t>NAHOMI ITZAYANA</t>
-  </si>
-  <si>
-    <t>YAIR DAVID</t>
-  </si>
-  <si>
-    <t>CRISTIAN MANUEL</t>
-  </si>
-  <si>
-    <t>ANGEL DE JESUS</t>
-  </si>
-  <si>
-    <t>LUZ AMELY</t>
-  </si>
-  <si>
-    <t>CRISTIAN JAHIR</t>
-  </si>
-  <si>
-    <t>SAID ANDRES</t>
-  </si>
-  <si>
-    <t>JOHAN ALEJANDRO</t>
-  </si>
-  <si>
-    <t>AMANDA MICHEL</t>
-  </si>
-  <si>
-    <t>VICTOR GAEL</t>
-  </si>
-  <si>
-    <t>JORGE ALEJANDRO</t>
-  </si>
-  <si>
-    <t>GONZALO FEDERICO</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>VICTOR GAMALIEL</t>
-  </si>
-  <si>
-    <t>CRISTIAN ARTURO</t>
-  </si>
-  <si>
-    <t>SUEMI</t>
-  </si>
-  <si>
-    <t>MELANIE NAOMI</t>
-  </si>
-  <si>
-    <t>JESUS</t>
   </si>
 </sst>
 </file>
@@ -744,19 +648,19 @@
         <v>27</v>
       </c>
       <c r="D2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G2">
-        <v>66.67</v>
+        <v>85.19</v>
       </c>
       <c r="H2">
-        <v>7.9</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -770,19 +674,19 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G3">
-        <v>83.33</v>
+        <v>94.44</v>
       </c>
       <c r="H3">
-        <v>8.300000000000001</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -796,19 +700,19 @@
         <v>36</v>
       </c>
       <c r="D4">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="G4">
-        <v>69.44</v>
+        <v>83.33</v>
       </c>
       <c r="H4">
-        <v>7.8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -822,19 +726,19 @@
         <v>33</v>
       </c>
       <c r="D5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F5">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G5">
-        <v>69.7</v>
+        <v>78.79000000000001</v>
       </c>
       <c r="H5">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -848,19 +752,19 @@
         <v>31</v>
       </c>
       <c r="D6">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G6">
-        <v>9.68</v>
+        <v>35.48</v>
       </c>
       <c r="H6">
-        <v>7.3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -874,19 +778,19 @@
         <v>34</v>
       </c>
       <c r="D7">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F7">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G7">
-        <v>67.65000000000001</v>
+        <v>76.47</v>
       </c>
       <c r="H7">
-        <v>7.7</v>
+        <v>6.8</v>
       </c>
     </row>
   </sheetData>
@@ -939,16 +843,19 @@
         <v>27</v>
       </c>
       <c r="D2">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>77.78</v>
+      </c>
+      <c r="H2">
+        <v>7.3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -962,16 +869,19 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>91.67</v>
+      </c>
+      <c r="H3">
+        <v>7.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -985,16 +895,19 @@
         <v>36</v>
       </c>
       <c r="D4">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>77.78</v>
+      </c>
+      <c r="H4">
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1008,16 +921,19 @@
         <v>33</v>
       </c>
       <c r="D5">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>72.73</v>
+      </c>
+      <c r="H5">
+        <v>6.8</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1031,16 +947,19 @@
         <v>31</v>
       </c>
       <c r="D6">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>32.26</v>
+      </c>
+      <c r="H6">
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1054,16 +973,19 @@
         <v>34</v>
       </c>
       <c r="D7">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>70.59</v>
+      </c>
+      <c r="H7">
+        <v>6.8</v>
       </c>
     </row>
   </sheetData>
@@ -1116,19 +1038,19 @@
         <v>27</v>
       </c>
       <c r="D2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G2">
-        <v>66.67</v>
+        <v>77.78</v>
       </c>
       <c r="H2">
-        <v>7.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1142,19 +1064,19 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G3">
-        <v>83.33</v>
+        <v>91.67</v>
       </c>
       <c r="H3">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1168,19 +1090,19 @@
         <v>36</v>
       </c>
       <c r="D4">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G4">
-        <v>69.44</v>
+        <v>77.78</v>
       </c>
       <c r="H4">
-        <v>7.8</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1194,19 +1116,19 @@
         <v>33</v>
       </c>
       <c r="D5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F5">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G5">
-        <v>69.7</v>
+        <v>72.73</v>
       </c>
       <c r="H5">
-        <v>7.6</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1220,19 +1142,19 @@
         <v>31</v>
       </c>
       <c r="D6">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G6">
-        <v>9.68</v>
+        <v>32.26</v>
       </c>
       <c r="H6">
-        <v>7.3</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1246,19 +1168,19 @@
         <v>34</v>
       </c>
       <c r="D7">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G7">
-        <v>67.65000000000001</v>
+        <v>70.59</v>
       </c>
       <c r="H7">
-        <v>7.7</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1268,7 +1190,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1300,16 +1222,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920051</v>
+        <v>20330051920087</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -1323,16 +1245,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920087</v>
+        <v>20330051920061</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D3" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -1346,16 +1268,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920091</v>
+        <v>20330051920065</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D4" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -1369,16 +1291,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920065</v>
+        <v>20330051920066</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="D5" t="s">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -1392,22 +1314,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920066</v>
+        <v>20330051920173</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="D6" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1415,22 +1337,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920068</v>
+        <v>20330051920126</v>
       </c>
       <c r="B7" t="s">
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D7" t="s">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1438,22 +1360,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920069</v>
+        <v>20330051920132</v>
       </c>
       <c r="B8" t="s">
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="D8" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1461,22 +1383,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920236</v>
+        <v>20330051920141</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="D9" t="s">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1484,22 +1406,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920157</v>
+        <v>20330051920145</v>
       </c>
       <c r="B10" t="s">
         <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="D10" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1507,22 +1429,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920388</v>
+        <v>20330051920148</v>
       </c>
       <c r="B11" t="s">
         <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="D11" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1530,22 +1452,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920137</v>
+        <v>20330051920039</v>
       </c>
       <c r="B12" t="s">
         <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D12" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -1553,22 +1475,19 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920141</v>
+        <v>20330051920099</v>
       </c>
       <c r="B13" t="s">
         <v>33</v>
       </c>
-      <c r="C13" t="s">
-        <v>61</v>
-      </c>
       <c r="D13" t="s">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G13">
         <v>2</v>
@@ -1576,59 +1495,62 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920387</v>
+        <v>21330051920335</v>
       </c>
       <c r="B14" t="s">
         <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="D14" t="s">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="E14" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920099</v>
+        <v>21330051920137</v>
       </c>
       <c r="B15" t="s">
         <v>35</v>
       </c>
+      <c r="C15" t="s">
+        <v>28</v>
+      </c>
       <c r="D15" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="E15" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G15">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920334</v>
+        <v>21330051920347</v>
       </c>
       <c r="B16" t="s">
         <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="D16" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1642,16 +1564,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920335</v>
+        <v>21330051920353</v>
       </c>
       <c r="B17" t="s">
         <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D17" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1665,22 +1587,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>21330051920336</v>
+        <v>19330051920051</v>
       </c>
       <c r="B18" t="s">
         <v>38</v>
       </c>
       <c r="C18" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D18" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="E18" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F18" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1688,22 +1610,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>21330051920341</v>
+        <v>20330051920063</v>
       </c>
       <c r="B19" t="s">
         <v>39</v>
       </c>
       <c r="C19" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D19" t="s">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="E19" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F19" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -1711,22 +1633,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>21330051920347</v>
+        <v>20330051920234</v>
       </c>
       <c r="B20" t="s">
         <v>40</v>
       </c>
       <c r="C20" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D20" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="E20" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F20" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -1734,346 +1656,24 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>21330051920348</v>
+        <v>20330051920387</v>
       </c>
       <c r="B21" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C21" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D21" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="E21" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F21" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>20330051920081</v>
-      </c>
-      <c r="B22" t="s">
-        <v>41</v>
-      </c>
-      <c r="C22" t="s">
-        <v>65</v>
-      </c>
-      <c r="D22" t="s">
-        <v>96</v>
-      </c>
-      <c r="E22" t="s">
-        <v>9</v>
-      </c>
-      <c r="F22" t="s">
-        <v>14</v>
-      </c>
-      <c r="G22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>20330051920082</v>
-      </c>
-      <c r="B23" t="s">
-        <v>41</v>
-      </c>
-      <c r="C23" t="s">
-        <v>66</v>
-      </c>
-      <c r="D23" t="s">
-        <v>97</v>
-      </c>
-      <c r="E23" t="s">
-        <v>9</v>
-      </c>
-      <c r="F23" t="s">
-        <v>14</v>
-      </c>
-      <c r="G23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>20330051920093</v>
-      </c>
-      <c r="B24" t="s">
-        <v>40</v>
-      </c>
-      <c r="C24" t="s">
-        <v>67</v>
-      </c>
-      <c r="D24" t="s">
-        <v>98</v>
-      </c>
-      <c r="E24" t="s">
-        <v>9</v>
-      </c>
-      <c r="F24" t="s">
-        <v>14</v>
-      </c>
-      <c r="G24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>20330051920062</v>
-      </c>
-      <c r="B25" t="s">
-        <v>42</v>
-      </c>
-      <c r="C25" t="s">
-        <v>68</v>
-      </c>
-      <c r="D25" t="s">
-        <v>99</v>
-      </c>
-      <c r="E25" t="s">
-        <v>9</v>
-      </c>
-      <c r="F25" t="s">
-        <v>14</v>
-      </c>
-      <c r="G25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>20330051920063</v>
-      </c>
-      <c r="B26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C26" t="s">
-        <v>69</v>
-      </c>
-      <c r="D26" t="s">
-        <v>100</v>
-      </c>
-      <c r="E26" t="s">
-        <v>9</v>
-      </c>
-      <c r="F26" t="s">
-        <v>14</v>
-      </c>
-      <c r="G26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>20330051920064</v>
-      </c>
-      <c r="B27" t="s">
-        <v>44</v>
-      </c>
-      <c r="C27" t="s">
-        <v>64</v>
-      </c>
-      <c r="D27" t="s">
-        <v>101</v>
-      </c>
-      <c r="E27" t="s">
-        <v>9</v>
-      </c>
-      <c r="F27" t="s">
-        <v>14</v>
-      </c>
-      <c r="G27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>20330051920234</v>
-      </c>
-      <c r="B28" t="s">
-        <v>45</v>
-      </c>
-      <c r="C28" t="s">
-        <v>70</v>
-      </c>
-      <c r="D28" t="s">
-        <v>102</v>
-      </c>
-      <c r="E28" t="s">
-        <v>9</v>
-      </c>
-      <c r="F28" t="s">
-        <v>11</v>
-      </c>
-      <c r="G28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>20330051920240</v>
-      </c>
-      <c r="B29" t="s">
-        <v>46</v>
-      </c>
-      <c r="C29" t="s">
-        <v>56</v>
-      </c>
-      <c r="D29" t="s">
-        <v>103</v>
-      </c>
-      <c r="E29" t="s">
-        <v>9</v>
-      </c>
-      <c r="F29" t="s">
-        <v>11</v>
-      </c>
-      <c r="G29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>20330051920244</v>
-      </c>
-      <c r="B30" t="s">
-        <v>47</v>
-      </c>
-      <c r="C30" t="s">
-        <v>71</v>
-      </c>
-      <c r="D30" t="s">
-        <v>104</v>
-      </c>
-      <c r="E30" t="s">
-        <v>9</v>
-      </c>
-      <c r="F30" t="s">
-        <v>11</v>
-      </c>
-      <c r="G30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>20330051920172</v>
-      </c>
-      <c r="B31" t="s">
-        <v>48</v>
-      </c>
-      <c r="C31" t="s">
-        <v>72</v>
-      </c>
-      <c r="D31" t="s">
-        <v>105</v>
-      </c>
-      <c r="E31" t="s">
-        <v>9</v>
-      </c>
-      <c r="F31" t="s">
-        <v>12</v>
-      </c>
-      <c r="G31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32">
-        <v>20330051920306</v>
-      </c>
-      <c r="B32" t="s">
-        <v>49</v>
-      </c>
-      <c r="C32" t="s">
-        <v>73</v>
-      </c>
-      <c r="D32" t="s">
-        <v>106</v>
-      </c>
-      <c r="E32" t="s">
-        <v>9</v>
-      </c>
-      <c r="F32" t="s">
-        <v>12</v>
-      </c>
-      <c r="G32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33">
-        <v>20330051920182</v>
-      </c>
-      <c r="B33" t="s">
-        <v>50</v>
-      </c>
-      <c r="C33" t="s">
-        <v>74</v>
-      </c>
-      <c r="D33" t="s">
-        <v>103</v>
-      </c>
-      <c r="E33" t="s">
-        <v>9</v>
-      </c>
-      <c r="F33" t="s">
-        <v>12</v>
-      </c>
-      <c r="G33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34">
-        <v>20330051920115</v>
-      </c>
-      <c r="B34" t="s">
-        <v>51</v>
-      </c>
-      <c r="C34" t="s">
-        <v>73</v>
-      </c>
-      <c r="D34" t="s">
-        <v>107</v>
-      </c>
-      <c r="E34" t="s">
-        <v>9</v>
-      </c>
-      <c r="F34" t="s">
-        <v>15</v>
-      </c>
-      <c r="G34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35">
-        <v>20330051920046</v>
-      </c>
-      <c r="B35" t="s">
-        <v>52</v>
-      </c>
-      <c r="C35" t="s">
-        <v>75</v>
-      </c>
-      <c r="D35" t="s">
-        <v>108</v>
-      </c>
-      <c r="E35" t="s">
-        <v>9</v>
-      </c>
-      <c r="F35" t="s">
-        <v>13</v>
-      </c>
-      <c r="G35">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Sánchez Rene Aurelio - Estadisticos 20212.xlsx
+++ b/docentes/González Sánchez Rene Aurelio - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="74">
   <si>
     <t>Mat</t>
   </si>
@@ -115,9 +115,6 @@
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
     <t>MENDIZABAL</t>
   </si>
   <si>
@@ -169,9 +166,6 @@
     <t>RAMON</t>
   </si>
   <si>
-    <t>CONCHE</t>
-  </si>
-  <si>
     <t>JUAREZ</t>
   </si>
   <si>
@@ -218,9 +212,6 @@
   </si>
   <si>
     <t>MEILYN ADABEL</t>
-  </si>
-  <si>
-    <t>GUSTAVO</t>
   </si>
   <si>
     <t>ALDER ALBERTO</t>
@@ -1190,7 +1181,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1231,7 +1222,7 @@
         <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -1251,10 +1242,10 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -1274,10 +1265,10 @@
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -1297,10 +1288,10 @@
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -1320,10 +1311,10 @@
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -1343,10 +1334,10 @@
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -1366,10 +1357,10 @@
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D8" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -1389,10 +1380,10 @@
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D9" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -1415,7 +1406,7 @@
         <v>28</v>
       </c>
       <c r="D10" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -1435,10 +1426,10 @@
         <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D11" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -1452,16 +1443,13 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920039</v>
+        <v>20330051920099</v>
       </c>
       <c r="B12" t="s">
         <v>32</v>
       </c>
-      <c r="C12" t="s">
-        <v>50</v>
-      </c>
       <c r="D12" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
@@ -1475,36 +1463,39 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920099</v>
+        <v>21330051920335</v>
       </c>
       <c r="B13" t="s">
         <v>33</v>
       </c>
+      <c r="C13" t="s">
+        <v>43</v>
+      </c>
       <c r="D13" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920335</v>
+        <v>21330051920137</v>
       </c>
       <c r="B14" t="s">
         <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="D14" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1518,16 +1509,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920137</v>
+        <v>21330051920347</v>
       </c>
       <c r="B15" t="s">
         <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="D15" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1541,16 +1532,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920347</v>
+        <v>21330051920353</v>
       </c>
       <c r="B16" t="s">
         <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D16" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1564,22 +1555,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920353</v>
+        <v>19330051920051</v>
       </c>
       <c r="B17" t="s">
         <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D17" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E17" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F17" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1587,16 +1578,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>19330051920051</v>
+        <v>20330051920063</v>
       </c>
       <c r="B18" t="s">
         <v>38</v>
       </c>
       <c r="C18" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D18" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E18" t="s">
         <v>9</v>
@@ -1610,22 +1601,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>20330051920063</v>
+        <v>20330051920234</v>
       </c>
       <c r="B19" t="s">
         <v>39</v>
       </c>
       <c r="C19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D19" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E19" t="s">
         <v>9</v>
       </c>
       <c r="F19" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -1633,47 +1624,24 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>20330051920234</v>
+        <v>20330051920387</v>
       </c>
       <c r="B20" t="s">
         <v>40</v>
       </c>
       <c r="C20" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D20" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E20" t="s">
         <v>9</v>
       </c>
       <c r="F20" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>20330051920387</v>
-      </c>
-      <c r="B21" t="s">
-        <v>41</v>
-      </c>
-      <c r="C21" t="s">
-        <v>56</v>
-      </c>
-      <c r="D21" t="s">
-        <v>76</v>
-      </c>
-      <c r="E21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" t="s">
-        <v>15</v>
-      </c>
-      <c r="G21">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Sánchez Rene Aurelio - Estadisticos 20212.xlsx
+++ b/docentes/González Sánchez Rene Aurelio - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="77">
   <si>
     <t>Mat</t>
   </si>
@@ -85,6 +85,9 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>CANUTO</t>
+  </si>
+  <si>
     <t>MARROQUIN</t>
   </si>
   <si>
@@ -106,40 +109,43 @@
     <t>LOPEZ</t>
   </si>
   <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>MENDIZABAL</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
+    <t>LARRINAGA</t>
+  </si>
+  <si>
     <t>OSORIO</t>
   </si>
   <si>
-    <t>RUIZ</t>
+    <t>ROSAS</t>
   </si>
   <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>MENDIZABAL</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
-    <t>LARRINAGA</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
+    <t>MEDINA</t>
   </si>
   <si>
     <t>IXMATLAHUA</t>
@@ -160,28 +166,31 @@
     <t>NOYOLA</t>
   </si>
   <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>CORONA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>SALAS</t>
+  </si>
+  <si>
+    <t>SANTES</t>
+  </si>
+  <si>
     <t>MACHORRO</t>
   </si>
   <si>
+    <t>SALAZAR</t>
+  </si>
+  <si>
     <t>RAMON</t>
   </si>
   <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>CORONA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>SALAS</t>
-  </si>
-  <si>
-    <t>SANTES</t>
-  </si>
-  <si>
-    <t>SALAZAR</t>
+    <t>ISRAEL</t>
   </si>
   <si>
     <t>GABRIEL JOSUE</t>
@@ -205,40 +214,40 @@
     <t>MARIA JOSE</t>
   </si>
   <si>
+    <t>XIMENA MICHELL</t>
+  </si>
+  <si>
+    <t>ALDER ALBERTO</t>
+  </si>
+  <si>
+    <t>NAHOMI ITZAYANA</t>
+  </si>
+  <si>
+    <t>GAEL JARED</t>
+  </si>
+  <si>
+    <t>ANGEL DE JESUS</t>
+  </si>
+  <si>
+    <t>ABIGAIL</t>
+  </si>
+  <si>
+    <t>JESUS ISRAEL</t>
+  </si>
+  <si>
+    <t>VICTOR GAEL</t>
+  </si>
+  <si>
+    <t>GONZALO FEDERICO</t>
+  </si>
+  <si>
     <t>KARLA</t>
   </si>
   <si>
-    <t>XIMENA MICHELL</t>
+    <t>MARIA FERNANDA</t>
   </si>
   <si>
     <t>MEILYN ADABEL</t>
-  </si>
-  <si>
-    <t>ALDER ALBERTO</t>
-  </si>
-  <si>
-    <t>NAHOMI ITZAYANA</t>
-  </si>
-  <si>
-    <t>GAEL JARED</t>
-  </si>
-  <si>
-    <t>ANGEL DE JESUS</t>
-  </si>
-  <si>
-    <t>ABIGAIL</t>
-  </si>
-  <si>
-    <t>JESUS ISRAEL</t>
-  </si>
-  <si>
-    <t>VICTOR GAEL</t>
-  </si>
-  <si>
-    <t>GONZALO FEDERICO</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
   </si>
 </sst>
 </file>
@@ -1181,7 +1190,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1213,16 +1222,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920087</v>
+        <v>20330051920073</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="D2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -1236,16 +1245,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920061</v>
+        <v>20330051920087</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -1259,16 +1268,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920065</v>
+        <v>20330051920061</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -1282,16 +1291,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920066</v>
+        <v>20330051920065</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -1305,22 +1314,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920173</v>
+        <v>20330051920066</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1328,22 +1337,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920126</v>
+        <v>20330051920173</v>
       </c>
       <c r="B7" t="s">
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1351,16 +1360,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920132</v>
+        <v>20330051920126</v>
       </c>
       <c r="B8" t="s">
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D8" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -1374,16 +1383,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920141</v>
+        <v>20330051920132</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D9" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -1403,10 +1412,10 @@
         <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D10" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -1420,22 +1429,19 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920148</v>
+        <v>20330051920099</v>
       </c>
       <c r="B11" t="s">
         <v>31</v>
       </c>
-      <c r="C11" t="s">
-        <v>48</v>
-      </c>
       <c r="D11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1443,36 +1449,39 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920099</v>
+        <v>21330051920335</v>
       </c>
       <c r="B12" t="s">
         <v>32</v>
       </c>
+      <c r="C12" t="s">
+        <v>45</v>
+      </c>
       <c r="D12" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920335</v>
+        <v>21330051920137</v>
       </c>
       <c r="B13" t="s">
         <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="D13" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1486,16 +1495,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920137</v>
+        <v>21330051920347</v>
       </c>
       <c r="B14" t="s">
         <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="D14" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1509,16 +1518,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920347</v>
+        <v>21330051920353</v>
       </c>
       <c r="B15" t="s">
         <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D15" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1532,22 +1541,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920353</v>
+        <v>19330051920051</v>
       </c>
       <c r="B16" t="s">
         <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D16" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E16" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F16" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1555,16 +1564,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>19330051920051</v>
+        <v>20330051920063</v>
       </c>
       <c r="B17" t="s">
         <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D17" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E17" t="s">
         <v>9</v>
@@ -1578,22 +1587,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>20330051920063</v>
+        <v>20330051920234</v>
       </c>
       <c r="B18" t="s">
         <v>38</v>
       </c>
       <c r="C18" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D18" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E18" t="s">
         <v>9</v>
       </c>
       <c r="F18" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1601,22 +1610,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>20330051920234</v>
+        <v>20330051920141</v>
       </c>
       <c r="B19" t="s">
         <v>39</v>
       </c>
       <c r="C19" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D19" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E19" t="s">
         <v>9</v>
       </c>
       <c r="F19" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -1630,10 +1639,10 @@
         <v>40</v>
       </c>
       <c r="C20" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D20" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E20" t="s">
         <v>9</v>
@@ -1642,6 +1651,29 @@
         <v>15</v>
       </c>
       <c r="G20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>20330051920148</v>
+      </c>
+      <c r="B21" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21" t="s">
+        <v>56</v>
+      </c>
+      <c r="D21" t="s">
+        <v>76</v>
+      </c>
+      <c r="E21" t="s">
+        <v>9</v>
+      </c>
+      <c r="F21" t="s">
+        <v>15</v>
+      </c>
+      <c r="G21">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Sánchez Rene Aurelio - Estadisticos 20212.xlsx
+++ b/docentes/González Sánchez Rene Aurelio - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="28">
   <si>
     <t>Mat</t>
   </si>
@@ -85,169 +85,22 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>CANUTO</t>
-  </si>
-  <si>
-    <t>MARROQUIN</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>SILVESTRE</t>
-  </si>
-  <si>
     <t>MENDEZ</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>MENDIZABAL</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
-    <t>LARRINAGA</t>
-  </si>
-  <si>
-    <t>OSORIO</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>MEDINA</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>URBINA</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>NOYOLA</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>CORONA</t>
-  </si>
-  <si>
     <t>CRUZ</t>
   </si>
   <si>
-    <t>SALAS</t>
-  </si>
-  <si>
-    <t>SANTES</t>
-  </si>
-  <si>
-    <t>MACHORRO</t>
-  </si>
-  <si>
-    <t>SALAZAR</t>
-  </si>
-  <si>
-    <t>RAMON</t>
-  </si>
-  <si>
-    <t>ISRAEL</t>
-  </si>
-  <si>
-    <t>GABRIEL JOSUE</t>
-  </si>
-  <si>
-    <t>ALAN URIEL</t>
-  </si>
-  <si>
-    <t>ALDIR ADALBERTO</t>
-  </si>
-  <si>
-    <t>YAIR</t>
-  </si>
-  <si>
     <t>VANNIA GISELLE</t>
   </si>
   <si>
-    <t>ESMERALDA</t>
-  </si>
-  <si>
-    <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>XIMENA MICHELL</t>
-  </si>
-  <si>
-    <t>ALDER ALBERTO</t>
-  </si>
-  <si>
-    <t>NAHOMI ITZAYANA</t>
-  </si>
-  <si>
-    <t>GAEL JARED</t>
-  </si>
-  <si>
-    <t>ANGEL DE JESUS</t>
-  </si>
-  <si>
-    <t>ABIGAIL</t>
-  </si>
-  <si>
     <t>JESUS ISRAEL</t>
-  </si>
-  <si>
-    <t>VICTOR GAEL</t>
-  </si>
-  <si>
-    <t>GONZALO FEDERICO</t>
-  </si>
-  <si>
-    <t>KARLA</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>MEILYN ADABEL</t>
   </si>
 </sst>
 </file>
@@ -1041,16 +894,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="G2">
-        <v>77.78</v>
+        <v>96.3</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1067,16 +920,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G3">
-        <v>91.67</v>
+        <v>97.22</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1093,16 +946,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="G4">
-        <v>77.78</v>
+        <v>91.67</v>
       </c>
       <c r="H4">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1119,13 +972,13 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G5">
-        <v>72.73</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="H5">
         <v>6.7</v>
@@ -1145,16 +998,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="G6">
-        <v>32.26</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="H6">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1171,16 +1024,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="G7">
-        <v>70.59</v>
+        <v>94.12</v>
       </c>
       <c r="H7">
-        <v>7</v>
+        <v>7.4</v>
       </c>
     </row>
   </sheetData>
@@ -1190,7 +1043,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1222,22 +1075,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920073</v>
+        <v>20330051920173</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>57</v>
+        <v>26</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1245,16 +1098,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920087</v>
+        <v>19330051920051</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -1263,417 +1116,6 @@
         <v>14</v>
       </c>
       <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>20330051920061</v>
-      </c>
-      <c r="B4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>20330051920065</v>
-      </c>
-      <c r="B5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D5" t="s">
-        <v>60</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>20330051920066</v>
-      </c>
-      <c r="B6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" t="s">
-        <v>45</v>
-      </c>
-      <c r="D6" t="s">
-        <v>61</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>20330051920173</v>
-      </c>
-      <c r="B7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" t="s">
-        <v>46</v>
-      </c>
-      <c r="D7" t="s">
-        <v>62</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>20330051920126</v>
-      </c>
-      <c r="B8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" t="s">
-        <v>47</v>
-      </c>
-      <c r="D8" t="s">
-        <v>63</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>20330051920132</v>
-      </c>
-      <c r="B9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" t="s">
-        <v>48</v>
-      </c>
-      <c r="D9" t="s">
-        <v>64</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>20330051920145</v>
-      </c>
-      <c r="B10" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10" t="s">
-        <v>65</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>20330051920099</v>
-      </c>
-      <c r="B11" t="s">
-        <v>31</v>
-      </c>
-      <c r="D11" t="s">
-        <v>66</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>13</v>
-      </c>
-      <c r="G11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>21330051920335</v>
-      </c>
-      <c r="B12" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" t="s">
-        <v>45</v>
-      </c>
-      <c r="D12" t="s">
-        <v>67</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>21330051920137</v>
-      </c>
-      <c r="B13" t="s">
-        <v>33</v>
-      </c>
-      <c r="C13" t="s">
-        <v>29</v>
-      </c>
-      <c r="D13" t="s">
-        <v>68</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>10</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>21330051920347</v>
-      </c>
-      <c r="B14" t="s">
-        <v>34</v>
-      </c>
-      <c r="C14" t="s">
-        <v>49</v>
-      </c>
-      <c r="D14" t="s">
-        <v>69</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>10</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>21330051920353</v>
-      </c>
-      <c r="B15" t="s">
-        <v>35</v>
-      </c>
-      <c r="C15" t="s">
-        <v>50</v>
-      </c>
-      <c r="D15" t="s">
-        <v>70</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>10</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>19330051920051</v>
-      </c>
-      <c r="B16" t="s">
-        <v>36</v>
-      </c>
-      <c r="C16" t="s">
-        <v>51</v>
-      </c>
-      <c r="D16" t="s">
-        <v>71</v>
-      </c>
-      <c r="E16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" t="s">
-        <v>14</v>
-      </c>
-      <c r="G16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>20330051920063</v>
-      </c>
-      <c r="B17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C17" t="s">
-        <v>52</v>
-      </c>
-      <c r="D17" t="s">
-        <v>72</v>
-      </c>
-      <c r="E17" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" t="s">
-        <v>14</v>
-      </c>
-      <c r="G17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>20330051920234</v>
-      </c>
-      <c r="B18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C18" t="s">
-        <v>53</v>
-      </c>
-      <c r="D18" t="s">
-        <v>73</v>
-      </c>
-      <c r="E18" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" t="s">
-        <v>11</v>
-      </c>
-      <c r="G18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>20330051920141</v>
-      </c>
-      <c r="B19" t="s">
-        <v>39</v>
-      </c>
-      <c r="C19" t="s">
-        <v>54</v>
-      </c>
-      <c r="D19" t="s">
-        <v>74</v>
-      </c>
-      <c r="E19" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" t="s">
-        <v>15</v>
-      </c>
-      <c r="G19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>20330051920387</v>
-      </c>
-      <c r="B20" t="s">
-        <v>40</v>
-      </c>
-      <c r="C20" t="s">
-        <v>55</v>
-      </c>
-      <c r="D20" t="s">
-        <v>75</v>
-      </c>
-      <c r="E20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20" t="s">
-        <v>15</v>
-      </c>
-      <c r="G20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>20330051920148</v>
-      </c>
-      <c r="B21" t="s">
-        <v>41</v>
-      </c>
-      <c r="C21" t="s">
-        <v>56</v>
-      </c>
-      <c r="D21" t="s">
-        <v>76</v>
-      </c>
-      <c r="E21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" t="s">
-        <v>15</v>
-      </c>
-      <c r="G21">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Sánchez Rene Aurelio - Estadisticos 20212.xlsx
+++ b/docentes/González Sánchez Rene Aurelio - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="25">
   <si>
     <t>Mat</t>
   </si>
@@ -85,19 +85,10 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
     <t>CRUZ</t>
-  </si>
-  <si>
-    <t>VANNIA GISELLE</t>
   </si>
   <si>
     <t>JESUS ISRAEL</t>
@@ -1043,7 +1034,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1075,47 +1066,24 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920173</v>
+        <v>19330051920051</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" t="s">
         <v>24</v>
       </c>
-      <c r="D2" t="s">
-        <v>26</v>
-      </c>
       <c r="E2" t="s">
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>19330051920051</v>
-      </c>
-      <c r="B3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Sánchez Rene Aurelio - Estadisticos 20212.xlsx
+++ b/docentes/González Sánchez Rene Aurelio - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="36">
   <si>
     <t>Mat</t>
   </si>
@@ -85,13 +85,46 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
+    <t>MARROQUIN</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>CERVANTES</t>
+  </si>
+  <si>
     <t>CRUZ</t>
   </si>
   <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>MARCO ANTONIO</t>
+  </si>
+  <si>
+    <t>AYLIN MELISSA</t>
+  </si>
+  <si>
+    <t>JAVIER</t>
+  </si>
+  <si>
     <t>JESUS ISRAEL</t>
+  </si>
+  <si>
+    <t>ESMERALDA</t>
   </si>
 </sst>
 </file>
@@ -1034,7 +1067,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1066,16 +1099,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920051</v>
+        <v>20330051920071</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -1084,6 +1117,98 @@
         <v>14</v>
       </c>
       <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>20330051920069</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>20330051920122</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>19330051920051</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>20330051920135</v>
+      </c>
+      <c r="B6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6">
         <v>1</v>
       </c>
     </row>
